--- a/FindingOrphanSources/Orphan Report for Gred on 9.24 in excel.xlsx
+++ b/FindingOrphanSources/Orphan Report for Gred on 9.24 in excel.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nyehealth-my.sharepoint.com/personal/mberger_nyehealth_org/Documents/Documents/code/SQLForS3InventoryOfPDR/FindingOrphanSources/"/>
@@ -18,7 +18,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-09-24-REPORT on All source'!$A$1:$F$681</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -907,30 +923,66 @@
     <t>RR153</t>
   </si>
   <si>
+    <t>QE</t>
+  </si>
+  <si>
+    <t>JSON &lt;&gt; when submitting</t>
+  </si>
+  <si>
     <t>RR811</t>
   </si>
   <si>
+    <t>soruce</t>
+  </si>
+  <si>
     <t>UR2536</t>
   </si>
   <si>
+    <t>MRN</t>
+  </si>
+  <si>
+    <t>HTTP: //POST</t>
+  </si>
+  <si>
     <t>RR810</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
     <t>PLLC</t>
   </si>
   <si>
+    <t>part 2</t>
+  </si>
+  <si>
     <t>RR102</t>
   </si>
   <si>
+    <t>DOCUMENT TYPE</t>
+  </si>
+  <si>
     <t>RR812</t>
   </si>
   <si>
+    <t>2 more mike forgets</t>
+  </si>
+  <si>
     <t>UR2435</t>
   </si>
   <si>
     <t>UR2439</t>
   </si>
   <si>
+    <t>NEVER OPENED BY PDR</t>
+  </si>
+  <si>
+    <t>WHOLE FILE OBJECT</t>
+  </si>
+  <si>
+    <t>XML</t>
+  </si>
+  <si>
     <t>RR814</t>
   </si>
   <si>
@@ -2015,49 +2067,13 @@
   </si>
   <si>
     <t>GLP</t>
-  </si>
-  <si>
-    <t>QE</t>
-  </si>
-  <si>
-    <t>soruce</t>
-  </si>
-  <si>
-    <t>MRN</t>
-  </si>
-  <si>
-    <t>date</t>
-  </si>
-  <si>
-    <t>part 2</t>
-  </si>
-  <si>
-    <t>2 more mike forgets</t>
-  </si>
-  <si>
-    <t>JSON &lt;&gt; when submitting</t>
-  </si>
-  <si>
-    <t>DOCUMENT TYPE</t>
-  </si>
-  <si>
-    <t>WHOLE FILE OBJECT</t>
-  </si>
-  <si>
-    <t>HTTP: //POST</t>
-  </si>
-  <si>
-    <t>XML</t>
-  </si>
-  <si>
-    <t>NEVER OPENED BY PDR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2917,7 +2933,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10B9A78F-42A8-40B7-A3A1-63CB234C6C7F}">
   <dimension ref="A1:L681"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.140625" customWidth="1"/>
     <col min="2" max="2" width="72.7109375" customWidth="1"/>
@@ -2925,7 +2941,7 @@
     <col min="10" max="10" width="22.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2945,7 +2961,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -2965,7 +2981,7 @@
         <v>46286.889004629629</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -2985,7 +3001,7 @@
         <v>46286.94835648148</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -3005,7 +3021,7 @@
         <v>46238.630706018521</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -3025,7 +3041,7 @@
         <v>46286.613796296297</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -3045,7 +3061,7 @@
         <v>46266.743761574071</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -3065,7 +3081,7 @@
         <v>46286.599131944444</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -3085,7 +3101,7 @@
         <v>46266.660844907405</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -3105,7 +3121,7 @@
         <v>46266.687916666669</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -3125,7 +3141,7 @@
         <v>46266.830347222225</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -3145,7 +3161,7 @@
         <v>46286.599131944444</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -3165,7 +3181,7 @@
         <v>46266.673854166664</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -3185,7 +3201,7 @@
         <v>46266.506932870368</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -3205,7 +3221,7 @@
         <v>46266.69222222222</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -3225,7 +3241,7 @@
         <v>46266.836805555555</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>11</v>
       </c>
@@ -3245,7 +3261,7 @@
         <v>46266.839930555558</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>11</v>
       </c>
@@ -3265,7 +3281,7 @@
         <v>46266.631168981483</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>11</v>
       </c>
@@ -3285,7 +3301,7 @@
         <v>46266.663148148145</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>11</v>
       </c>
@@ -3305,7 +3321,7 @@
         <v>46266.841354166667</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -3325,7 +3341,7 @@
         <v>46266.834189814814</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>11</v>
       </c>
@@ -3345,7 +3361,7 @@
         <v>46266.841747685183</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -3365,7 +3381,7 @@
         <v>46266.661608796298</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>11</v>
       </c>
@@ -3385,7 +3401,7 @@
         <v>46266.748518518521</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -3405,7 +3421,7 @@
         <v>46266.838090277779</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>11</v>
       </c>
@@ -3425,7 +3441,7 @@
         <v>46266.747430555559</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>11</v>
       </c>
@@ -3445,7 +3461,7 @@
         <v>46175.605104166665</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -3465,7 +3481,7 @@
         <v>46270.634074074071</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>11</v>
       </c>
@@ -3485,7 +3501,7 @@
         <v>46265.925763888888</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>11</v>
       </c>
@@ -3505,7 +3521,7 @@
         <v>46265.937268518515</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>11</v>
       </c>
@@ -3525,7 +3541,7 @@
         <v>46265.947025462963</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>11</v>
       </c>
@@ -3545,7 +3561,7 @@
         <v>46266.51017361111</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>11</v>
       </c>
@@ -3565,7 +3581,7 @@
         <v>46266.513553240744</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>11</v>
       </c>
@@ -3585,7 +3601,7 @@
         <v>46266.520532407405</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>11</v>
       </c>
@@ -3605,7 +3621,7 @@
         <v>46266.746782407405</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>13</v>
       </c>
@@ -3625,7 +3641,7 @@
         <v>46275.773518518516</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>13</v>
       </c>
@@ -3645,7 +3661,7 @@
         <v>46275.773518518516</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>13</v>
       </c>
@@ -3665,7 +3681,7 @@
         <v>46275.773506944446</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>13</v>
       </c>
@@ -3685,7 +3701,7 @@
         <v>46275.7734837963</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>13</v>
       </c>
@@ -3705,7 +3721,7 @@
         <v>46275.773530092592</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -3725,7 +3741,7 @@
         <v>46275.773379629631</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>13</v>
       </c>
@@ -3745,7 +3761,7 @@
         <v>46275.77138888889</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>13</v>
       </c>
@@ -3765,7 +3781,7 @@
         <v>46274.393877314818</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>13</v>
       </c>
@@ -3785,7 +3801,7 @@
         <v>46274.394270833334</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>13</v>
       </c>
@@ -3805,7 +3821,7 @@
         <v>46274.394247685188</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>13</v>
       </c>
@@ -3825,7 +3841,7 @@
         <v>46274.394062500003</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -3845,7 +3861,7 @@
         <v>46274.394085648149</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>13</v>
       </c>
@@ -3865,7 +3881,7 @@
         <v>46274.393993055557</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>13</v>
       </c>
@@ -3885,7 +3901,7 @@
         <v>46286.99894675926</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>13</v>
       </c>
@@ -3905,7 +3921,7 @@
         <v>46275.271099537036</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>13</v>
       </c>
@@ -3925,7 +3941,7 @@
         <v>46275.26835648148</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>13</v>
       </c>
@@ -3945,7 +3961,7 @@
         <v>46282.73505787037</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>13</v>
       </c>
@@ -3965,7 +3981,7 @@
         <v>46274.39403935185</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>13</v>
       </c>
@@ -3985,7 +4001,7 @@
         <v>46274.394155092596</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>13</v>
       </c>
@@ -4005,7 +4021,7 @@
         <v>46274.378738425927</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>13</v>
       </c>
@@ -4025,7 +4041,7 @@
         <v>46274.394166666665</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>13</v>
       </c>
@@ -4045,7 +4061,7 @@
         <v>46274.378321759257</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>13</v>
       </c>
@@ -4065,7 +4081,7 @@
         <v>46274.394004629627</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -4085,7 +4101,7 @@
         <v>46274.393796296295</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>13</v>
       </c>
@@ -4105,7 +4121,7 @@
         <v>46273.032673611109</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>13</v>
       </c>
@@ -4125,7 +4141,7 @@
         <v>46274.39403935185</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>13</v>
       </c>
@@ -4145,7 +4161,7 @@
         <v>46274.390335648146</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>13</v>
       </c>
@@ -4165,7 +4181,7 @@
         <v>46274.386400462965</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>13</v>
       </c>
@@ -4185,7 +4201,7 @@
         <v>46274.393842592595</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>13</v>
       </c>
@@ -4205,7 +4221,7 @@
         <v>46274.389918981484</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6">
       <c r="A65" t="s">
         <v>13</v>
       </c>
@@ -4225,7 +4241,7 @@
         <v>46274.389826388891</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6">
       <c r="A66" t="s">
         <v>13</v>
       </c>
@@ -4245,7 +4261,7 @@
         <v>46274.386388888888</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6">
       <c r="A67" t="s">
         <v>13</v>
       </c>
@@ -4265,7 +4281,7 @@
         <v>46275.30704861111</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6">
       <c r="A68" t="s">
         <v>13</v>
       </c>
@@ -4285,7 +4301,7 @@
         <v>46274.38616898148</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6">
       <c r="A69" t="s">
         <v>13</v>
       </c>
@@ -4305,7 +4321,7 @@
         <v>46274.394097222219</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6">
       <c r="A70" t="s">
         <v>13</v>
       </c>
@@ -4325,7 +4341,7 @@
         <v>46274.386030092595</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6">
       <c r="A71" t="s">
         <v>13</v>
       </c>
@@ -4345,7 +4361,7 @@
         <v>46274.382534722223</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6">
       <c r="A72" t="s">
         <v>13</v>
       </c>
@@ -4365,7 +4381,7 @@
         <v>46274.393807870372</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6">
       <c r="A73" t="s">
         <v>13</v>
       </c>
@@ -4385,7 +4401,7 @@
         <v>46274.390300925923</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6">
       <c r="A74" t="s">
         <v>13</v>
       </c>
@@ -4405,7 +4421,7 @@
         <v>46274.386493055557</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6">
       <c r="A75" t="s">
         <v>13</v>
       </c>
@@ -4425,7 +4441,7 @@
         <v>46274.393935185188</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6">
       <c r="A76" t="s">
         <v>13</v>
       </c>
@@ -4445,7 +4461,7 @@
         <v>46274.390324074076</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6">
       <c r="A77" t="s">
         <v>13</v>
       </c>
@@ -4465,7 +4481,7 @@
         <v>46275.307037037041</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6">
       <c r="A78" t="s">
         <v>13</v>
       </c>
@@ -4485,7 +4501,7 @@
         <v>46275.295810185184</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6">
       <c r="A79" t="s">
         <v>13</v>
       </c>
@@ -4505,7 +4521,7 @@
         <v>46274.374293981484</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6">
       <c r="A80" t="s">
         <v>13</v>
       </c>
@@ -4525,7 +4541,7 @@
         <v>46274.358773148146</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6">
       <c r="A81" t="s">
         <v>13</v>
       </c>
@@ -4545,7 +4561,7 @@
         <v>46274.389918981484</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6">
       <c r="A82" t="s">
         <v>13</v>
       </c>
@@ -4565,7 +4581,7 @@
         <v>46172.463923611111</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6">
       <c r="A83" t="s">
         <v>13</v>
       </c>
@@ -4585,7 +4601,7 @@
         <v>46286.899247685185</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6">
       <c r="A84" t="s">
         <v>13</v>
       </c>
@@ -4605,7 +4621,7 @@
         <v>46274.382303240738</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6">
       <c r="A85" t="s">
         <v>13</v>
       </c>
@@ -4625,7 +4641,7 @@
         <v>46274.382372685184</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6">
       <c r="A86" t="s">
         <v>13</v>
       </c>
@@ -4645,7 +4661,7 @@
         <v>46273.368842592594</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6">
       <c r="A87" t="s">
         <v>13</v>
       </c>
@@ -4665,7 +4681,7 @@
         <v>46274.385983796295</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6">
       <c r="A88" t="s">
         <v>13</v>
       </c>
@@ -4685,7 +4701,7 @@
         <v>46273.384016203701</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6">
       <c r="A89" t="s">
         <v>13</v>
       </c>
@@ -4705,7 +4721,7 @@
         <v>46274.390231481484</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6">
       <c r="A90" t="s">
         <v>13</v>
       </c>
@@ -4725,7 +4741,7 @@
         <v>46274.393958333334</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6">
       <c r="A91" t="s">
         <v>13</v>
       </c>
@@ -4745,7 +4761,7 @@
         <v>46271.312303240738</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6">
       <c r="A92" t="s">
         <v>13</v>
       </c>
@@ -4765,7 +4781,7 @@
         <v>46272.910439814812</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6">
       <c r="A93" t="s">
         <v>13</v>
       </c>
@@ -4785,7 +4801,7 @@
         <v>46274.367037037038</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6">
       <c r="A94" t="s">
         <v>13</v>
       </c>
@@ -4805,7 +4821,7 @@
         <v>46274.374699074076</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6">
       <c r="A95" t="s">
         <v>13</v>
       </c>
@@ -4825,7 +4841,7 @@
         <v>46274.389930555553</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6">
       <c r="A96" t="s">
         <v>13</v>
       </c>
@@ -4845,7 +4861,7 @@
         <v>46274.390405092592</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6">
       <c r="A97" t="s">
         <v>13</v>
       </c>
@@ -4865,7 +4881,7 @@
         <v>46274.331400462965</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6">
       <c r="A98" t="s">
         <v>13</v>
       </c>
@@ -4885,7 +4901,7 @@
         <v>46274.382268518515</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6">
       <c r="A99" t="s">
         <v>13</v>
       </c>
@@ -4905,7 +4921,7 @@
         <v>46274.394016203703</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6">
       <c r="A100" t="s">
         <v>13</v>
       </c>
@@ -4925,7 +4941,7 @@
         <v>46275.271134259259</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6">
       <c r="A101" t="s">
         <v>13</v>
       </c>
@@ -4945,7 +4961,7 @@
         <v>46274.386238425926</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6">
       <c r="A102" t="s">
         <v>13</v>
       </c>
@@ -4965,7 +4981,7 @@
         <v>46272.950601851851</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6">
       <c r="A103" t="s">
         <v>13</v>
       </c>
@@ -4985,7 +5001,7 @@
         <v>46274.389907407407</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6">
       <c r="A104" t="s">
         <v>13</v>
       </c>
@@ -5005,7 +5021,7 @@
         <v>46274.3591087963</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6">
       <c r="A105" t="s">
         <v>13</v>
       </c>
@@ -5025,7 +5041,7 @@
         <v>46273.376539351855</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6">
       <c r="A106" t="s">
         <v>13</v>
       </c>
@@ -5045,7 +5061,7 @@
         <v>46273.384386574071</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6">
       <c r="A107" t="s">
         <v>13</v>
       </c>
@@ -5065,7 +5081,7 @@
         <v>46274.389849537038</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6">
       <c r="A108" t="s">
         <v>13</v>
       </c>
@@ -5085,7 +5101,7 @@
         <v>46266.333043981482</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6">
       <c r="A109" t="s">
         <v>13</v>
       </c>
@@ -5105,7 +5121,7 @@
         <v>46275.730474537035</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6">
       <c r="A110" t="s">
         <v>13</v>
       </c>
@@ -5125,7 +5141,7 @@
         <v>46284.262326388889</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6">
       <c r="A111" t="s">
         <v>13</v>
       </c>
@@ -5145,7 +5161,7 @@
         <v>46274.359097222223</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6">
       <c r="A112" t="s">
         <v>13</v>
       </c>
@@ -5165,7 +5181,7 @@
         <v>46273.009814814817</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>13</v>
       </c>
@@ -5185,7 +5201,7 @@
         <v>46272.922627314816</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>13</v>
       </c>
@@ -5205,7 +5221,7 @@
         <v>46274.817523148151</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>13</v>
       </c>
@@ -5225,7 +5241,7 @@
         <v>46149.233738425923</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>13</v>
       </c>
@@ -5245,7 +5261,7 @@
         <v>46274.386493055557</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>13</v>
       </c>
@@ -5265,7 +5281,7 @@
         <v>46275.736585648148</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>13</v>
       </c>
@@ -5285,7 +5301,7 @@
         <v>46275.271134259259</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>13</v>
       </c>
@@ -5305,7 +5321,7 @@
         <v>46275.757824074077</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>13</v>
       </c>
@@ -5325,7 +5341,7 @@
         <v>46275.656747685185</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>13</v>
       </c>
@@ -5345,7 +5361,7 @@
         <v>46275.727731481478</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>13</v>
       </c>
@@ -5365,7 +5381,7 @@
         <v>46275.688379629632</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>13</v>
       </c>
@@ -5385,7 +5401,7 @@
         <v>46275.747372685182</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>13</v>
       </c>
@@ -5405,7 +5421,7 @@
         <v>46275.772800925923</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>13</v>
       </c>
@@ -5425,7 +5441,7 @@
         <v>46272.985636574071</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>13</v>
       </c>
@@ -5445,7 +5461,7 @@
         <v>46272.985729166663</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>13</v>
       </c>
@@ -5465,7 +5481,7 @@
         <v>46275.271111111113</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>13</v>
       </c>
@@ -5485,7 +5501,7 @@
         <v>46274.389976851853</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6">
       <c r="A129" t="s">
         <v>13</v>
       </c>
@@ -5505,7 +5521,7 @@
         <v>46236.772800925923</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6">
       <c r="A130" t="s">
         <v>13</v>
       </c>
@@ -5525,7 +5541,7 @@
         <v>46272.950173611112</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6">
       <c r="A131" t="s">
         <v>13</v>
       </c>
@@ -5545,7 +5561,7 @@
         <v>46275.454699074071</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6">
       <c r="A132" t="s">
         <v>13</v>
       </c>
@@ -5565,7 +5581,7 @@
         <v>46275.607986111114</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6">
       <c r="A133" t="s">
         <v>13</v>
       </c>
@@ -5585,7 +5601,7 @@
         <v>46272.875462962962</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6">
       <c r="A134" t="s">
         <v>13</v>
       </c>
@@ -5605,7 +5621,7 @@
         <v>46273.032870370371</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6">
       <c r="A135" t="s">
         <v>13</v>
       </c>
@@ -5625,7 +5641,7 @@
         <v>46274.393773148149</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6">
       <c r="A136" t="s">
         <v>13</v>
       </c>
@@ -5645,7 +5661,7 @@
         <v>46272.78460648148</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6">
       <c r="A137" t="s">
         <v>13</v>
       </c>
@@ -5665,7 +5681,7 @@
         <v>46286.992407407408</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6">
       <c r="A138" t="s">
         <v>13</v>
       </c>
@@ -5685,7 +5701,7 @@
         <v>46275.527615740742</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6">
       <c r="A139" t="s">
         <v>13</v>
       </c>
@@ -5705,7 +5721,7 @@
         <v>46275.7421875</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6">
       <c r="A140" t="s">
         <v>13</v>
       </c>
@@ -5725,7 +5741,7 @@
         <v>46273.349004629628</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6">
       <c r="A141" t="s">
         <v>13</v>
       </c>
@@ -5745,7 +5761,7 @@
         <v>46275.754432870373</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6">
       <c r="A142" t="s">
         <v>13</v>
       </c>
@@ -5765,7 +5781,7 @@
         <v>46275.753784722219</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6">
       <c r="A143" t="s">
         <v>13</v>
       </c>
@@ -5785,7 +5801,7 @@
         <v>46275.681446759256</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6">
       <c r="A144" t="s">
         <v>13</v>
       </c>
@@ -5805,7 +5821,7 @@
         <v>46275.103564814817</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6">
       <c r="A145" t="s">
         <v>13</v>
       </c>
@@ -5825,7 +5841,7 @@
         <v>46272.981435185182</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6">
       <c r="A146" t="s">
         <v>13</v>
       </c>
@@ -5845,7 +5861,7 @@
         <v>46274.984317129631</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6">
       <c r="A147" t="s">
         <v>13</v>
       </c>
@@ -5865,7 +5881,7 @@
         <v>46275.502627314818</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6">
       <c r="A148" t="s">
         <v>13</v>
       </c>
@@ -5885,7 +5901,7 @@
         <v>46275.731990740744</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6">
       <c r="A149" t="s">
         <v>13</v>
       </c>
@@ -5905,7 +5921,7 @@
         <v>46273.009594907409</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6">
       <c r="A150" t="s">
         <v>13</v>
       </c>
@@ -5925,7 +5941,7 @@
         <v>46275.662326388891</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6">
       <c r="A151" t="s">
         <v>13</v>
       </c>
@@ -5945,7 +5961,7 @@
         <v>46275.653993055559</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6">
       <c r="A152" t="s">
         <v>13</v>
       </c>
@@ -5965,7 +5981,7 @@
         <v>46275.753611111111</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6">
       <c r="A153" t="s">
         <v>13</v>
       </c>
@@ -5985,7 +6001,7 @@
         <v>46272.930717592593</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6">
       <c r="A154" t="s">
         <v>13</v>
       </c>
@@ -6005,7 +6021,7 @@
         <v>46275.634016203701</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6">
       <c r="A155" t="s">
         <v>13</v>
       </c>
@@ -6025,7 +6041,7 @@
         <v>46275.546111111114</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6">
       <c r="A156" t="s">
         <v>13</v>
       </c>
@@ -6045,7 +6061,7 @@
         <v>46275.754236111112</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:6">
       <c r="A157" t="s">
         <v>13</v>
       </c>
@@ -6065,7 +6081,7 @@
         <v>46275.649328703701</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6">
       <c r="A158" t="s">
         <v>13</v>
       </c>
@@ -6085,7 +6101,7 @@
         <v>46272.985925925925</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6">
       <c r="A159" t="s">
         <v>13</v>
       </c>
@@ -6105,7 +6121,7 @@
         <v>46275.767731481479</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6">
       <c r="A160" t="s">
         <v>13</v>
       </c>
@@ -6125,7 +6141,7 @@
         <v>46275.589907407404</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6">
       <c r="A161" t="s">
         <v>13</v>
       </c>
@@ -6145,7 +6161,7 @@
         <v>46275.706828703704</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6">
       <c r="A162" t="s">
         <v>13</v>
       </c>
@@ -6165,7 +6181,7 @@
         <v>46273.376307870371</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6">
       <c r="A163" t="s">
         <v>13</v>
       </c>
@@ -6185,7 +6201,7 @@
         <v>46274.926759259259</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6">
       <c r="A164" t="s">
         <v>13</v>
       </c>
@@ -6205,7 +6221,7 @@
         <v>46275.12641203704</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:6">
       <c r="A165" t="s">
         <v>13</v>
       </c>
@@ -6225,7 +6241,7 @@
         <v>46275.737615740742</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:6">
       <c r="A166" t="s">
         <v>13</v>
       </c>
@@ -6245,7 +6261,7 @@
         <v>46272.887013888889</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6">
       <c r="A167" t="s">
         <v>13</v>
       </c>
@@ -6265,7 +6281,7 @@
         <v>46275.44771990741</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6">
       <c r="A168" t="s">
         <v>13</v>
       </c>
@@ -6285,7 +6301,7 @@
         <v>46275.094594907408</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6">
       <c r="A169" t="s">
         <v>13</v>
       </c>
@@ -6305,7 +6321,7 @@
         <v>46274.860289351855</v>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:6">
       <c r="A170" t="s">
         <v>13</v>
       </c>
@@ -6325,7 +6341,7 @@
         <v>46272.780011574076</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6">
       <c r="A171" t="s">
         <v>13</v>
       </c>
@@ -6345,7 +6361,7 @@
         <v>46286.99454861111</v>
       </c>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:6">
       <c r="A172" t="s">
         <v>13</v>
       </c>
@@ -6365,7 +6381,7 @@
         <v>46275.089918981481</v>
       </c>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:6">
       <c r="A173" t="s">
         <v>13</v>
       </c>
@@ -6385,7 +6401,7 @@
         <v>46205.202175925922</v>
       </c>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:6">
       <c r="A174" t="s">
         <v>13</v>
       </c>
@@ -6405,7 +6421,7 @@
         <v>46275.640763888892</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6">
       <c r="A175" t="s">
         <v>13</v>
       </c>
@@ -6425,7 +6441,7 @@
         <v>46272.265439814815</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6">
       <c r="A176" t="s">
         <v>13</v>
       </c>
@@ -6445,7 +6461,7 @@
         <v>46275.75209490741</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6">
       <c r="A177" t="s">
         <v>13</v>
       </c>
@@ -6465,7 +6481,7 @@
         <v>46275.62462962963</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6">
       <c r="A178" t="s">
         <v>13</v>
       </c>
@@ -6485,7 +6501,7 @@
         <v>46275.684537037036</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6">
       <c r="A179" t="s">
         <v>13</v>
       </c>
@@ -6505,7 +6521,7 @@
         <v>46275.749606481484</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6">
       <c r="A180" t="s">
         <v>13</v>
       </c>
@@ -6525,7 +6541,7 @@
         <v>46275.138402777775</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6">
       <c r="A181" t="s">
         <v>13</v>
       </c>
@@ -6545,7 +6561,7 @@
         <v>46275.736643518518</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6">
       <c r="A182" t="s">
         <v>13</v>
       </c>
@@ -6565,7 +6581,7 @@
         <v>46275.66</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6">
       <c r="A183" t="s">
         <v>13</v>
       </c>
@@ -6585,7 +6601,7 @@
         <v>46273.629837962966</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6">
       <c r="A184" t="s">
         <v>13</v>
       </c>
@@ -6605,7 +6621,7 @@
         <v>46274.403194444443</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6">
       <c r="A185" t="s">
         <v>13</v>
       </c>
@@ -6625,7 +6641,7 @@
         <v>46272.99790509259</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6">
       <c r="A186" t="s">
         <v>13</v>
       </c>
@@ -6645,7 +6661,7 @@
         <v>46274.986828703702</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6">
       <c r="A187" t="s">
         <v>13</v>
       </c>
@@ -6665,7 +6681,7 @@
         <v>46275.496168981481</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6">
       <c r="A188" t="s">
         <v>13</v>
       </c>
@@ -6685,7 +6701,7 @@
         <v>46275.296238425923</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6">
       <c r="A189" t="s">
         <v>13</v>
       </c>
@@ -6705,7 +6721,7 @@
         <v>46260.143888888888</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6">
       <c r="A190" t="s">
         <v>13</v>
       </c>
@@ -6725,7 +6741,7 @@
         <v>46274.728981481479</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6">
       <c r="A191" t="s">
         <v>13</v>
       </c>
@@ -6745,7 +6761,7 @@
         <v>46275.712951388887</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6">
       <c r="A192" t="s">
         <v>13</v>
       </c>
@@ -6765,7 +6781,7 @@
         <v>46275.603460648148</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6">
       <c r="A193" t="s">
         <v>13</v>
       </c>
@@ -6785,7 +6801,7 @@
         <v>46275.575648148151</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6">
       <c r="A194" t="s">
         <v>13</v>
       </c>
@@ -6805,7 +6821,7 @@
         <v>46275.664837962962</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6">
       <c r="A195" t="s">
         <v>13</v>
       </c>
@@ -6825,7 +6841,7 @@
         <v>46271.313252314816</v>
       </c>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:6">
       <c r="A196" t="s">
         <v>13</v>
       </c>
@@ -6845,7 +6861,7 @@
         <v>46275.576342592591</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6">
       <c r="A197" t="s">
         <v>13</v>
       </c>
@@ -6865,7 +6881,7 @@
         <v>46275.09652777778</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6">
       <c r="A198" t="s">
         <v>13</v>
       </c>
@@ -6885,7 +6901,7 @@
         <v>46275.447442129633</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6">
       <c r="A199" t="s">
         <v>13</v>
       </c>
@@ -6905,7 +6921,7 @@
         <v>46275.551064814812</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6">
       <c r="A200" t="s">
         <v>13</v>
       </c>
@@ -6925,7 +6941,7 @@
         <v>46274.301249999997</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6">
       <c r="A201" t="s">
         <v>13</v>
       </c>
@@ -6945,7 +6961,7 @@
         <v>46275.586006944446</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6">
       <c r="A202" t="s">
         <v>13</v>
       </c>
@@ -6965,7 +6981,7 @@
         <v>46274.832442129627</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6">
       <c r="A203" t="s">
         <v>13</v>
       </c>
@@ -6985,7 +7001,7 @@
         <v>46275.716736111113</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6">
       <c r="A204" t="s">
         <v>13</v>
       </c>
@@ -7005,7 +7021,7 @@
         <v>46275.687280092592</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6">
       <c r="A205" t="s">
         <v>13</v>
       </c>
@@ -7025,7 +7041,7 @@
         <v>46275.673171296294</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -7045,7 +7061,7 @@
         <v>46275.641226851854</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6">
       <c r="A207" t="s">
         <v>13</v>
       </c>
@@ -7065,7 +7081,7 @@
         <v>46275.674398148149</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6">
       <c r="A208" t="s">
         <v>13</v>
       </c>
@@ -7085,7 +7101,7 @@
         <v>46275.268263888887</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6">
       <c r="A209" t="s">
         <v>13</v>
       </c>
@@ -7105,7 +7121,7 @@
         <v>46275.538958333331</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6">
       <c r="A210" t="s">
         <v>13</v>
       </c>
@@ -7125,7 +7141,7 @@
         <v>46286.677870370368</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6">
       <c r="A211" t="s">
         <v>13</v>
       </c>
@@ -7145,7 +7161,7 @@
         <v>46272.692962962959</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6">
       <c r="A212" t="s">
         <v>13</v>
       </c>
@@ -7165,7 +7181,7 @@
         <v>46275.158912037034</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6">
       <c r="A213" t="s">
         <v>13</v>
       </c>
@@ -7185,7 +7201,7 @@
         <v>46275.268368055556</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6">
       <c r="A214" t="s">
         <v>13</v>
       </c>
@@ -7205,7 +7221,7 @@
         <v>46275.193541666667</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6">
       <c r="A215" t="s">
         <v>13</v>
       </c>
@@ -7225,7 +7241,7 @@
         <v>46275.609502314815</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6">
       <c r="A216" t="s">
         <v>13</v>
       </c>
@@ -7245,7 +7261,7 @@
         <v>46275.726157407407</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6">
       <c r="A217" t="s">
         <v>13</v>
       </c>
@@ -7265,7 +7281,7 @@
         <v>46274.684629629628</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6">
       <c r="A218" t="s">
         <v>13</v>
       </c>
@@ -7285,7 +7301,7 @@
         <v>46272.898958333331</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6">
       <c r="A219" t="s">
         <v>13</v>
       </c>
@@ -7305,7 +7321,7 @@
         <v>46273.372766203705</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6">
       <c r="A220" t="s">
         <v>13</v>
       </c>
@@ -7325,7 +7341,7 @@
         <v>46275.767893518518</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6">
       <c r="A221" t="s">
         <v>13</v>
       </c>
@@ -7345,7 +7361,7 @@
         <v>46275.622997685183</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6">
       <c r="A222" t="s">
         <v>13</v>
       </c>
@@ -7365,7 +7381,7 @@
         <v>46275.684374999997</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6">
       <c r="A223" t="s">
         <v>13</v>
       </c>
@@ -7385,7 +7401,7 @@
         <v>46274.378425925926</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6">
       <c r="A224" t="s">
         <v>13</v>
       </c>
@@ -7405,7 +7421,7 @@
         <v>46269.676238425927</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6">
       <c r="A225" t="s">
         <v>13</v>
       </c>
@@ -7425,7 +7441,7 @@
         <v>46275.576898148145</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6">
       <c r="A226" t="s">
         <v>13</v>
       </c>
@@ -7445,7 +7461,7 @@
         <v>46274.659074074072</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6">
       <c r="A227" t="s">
         <v>13</v>
       </c>
@@ -7465,7 +7481,7 @@
         <v>46273.847303240742</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6">
       <c r="A228" t="s">
         <v>13</v>
       </c>
@@ -7485,7 +7501,7 @@
         <v>46275.641238425924</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6">
       <c r="A229" t="s">
         <v>13</v>
       </c>
@@ -7505,7 +7521,7 @@
         <v>46275.271157407406</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6">
       <c r="A230" t="s">
         <v>13</v>
       </c>
@@ -7525,7 +7541,7 @@
         <v>46275.55537037037</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6">
       <c r="A231" t="s">
         <v>13</v>
       </c>
@@ -7545,7 +7561,7 @@
         <v>46160.831319444442</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6">
       <c r="A232" t="s">
         <v>13</v>
       </c>
@@ -7565,7 +7581,7 @@
         <v>46272.277488425927</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6">
       <c r="A233" t="s">
         <v>13</v>
       </c>
@@ -7585,7 +7601,7 @@
         <v>46275.511840277781</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6">
       <c r="A234" t="s">
         <v>13</v>
       </c>
@@ -7605,7 +7621,7 @@
         <v>46286.85796296296</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6">
       <c r="A235" t="s">
         <v>13</v>
       </c>
@@ -7625,7 +7641,7 @@
         <v>46275.124710648146</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6">
       <c r="A236" t="s">
         <v>13</v>
       </c>
@@ -7645,7 +7661,7 @@
         <v>46274.756701388891</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6">
       <c r="A237" t="s">
         <v>13</v>
       </c>
@@ -7665,7 +7681,7 @@
         <v>46256.290937500002</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6">
       <c r="A238" t="s">
         <v>13</v>
       </c>
@@ -7685,7 +7701,7 @@
         <v>46286.94290509259</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6">
       <c r="A239" t="s">
         <v>13</v>
       </c>
@@ -7705,7 +7721,7 @@
         <v>46272.585462962961</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6">
       <c r="A240" t="s">
         <v>13</v>
       </c>
@@ -7725,7 +7741,7 @@
         <v>46275.268194444441</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6">
       <c r="A241" t="s">
         <v>13</v>
       </c>
@@ -7745,7 +7761,7 @@
         <v>46272.993807870371</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6">
       <c r="A242" t="s">
         <v>13</v>
       </c>
@@ -7765,7 +7781,7 @@
         <v>46272.622337962966</v>
       </c>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:6">
       <c r="A243" t="s">
         <v>13</v>
       </c>
@@ -7785,7 +7801,7 @@
         <v>46272.922615740739</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6">
       <c r="A244" t="s">
         <v>13</v>
       </c>
@@ -7805,7 +7821,7 @@
         <v>46286.895208333335</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6">
       <c r="A245" t="s">
         <v>13</v>
       </c>
@@ -7825,7 +7841,7 @@
         <v>46244.517685185187</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6">
       <c r="A246" t="s">
         <v>13</v>
       </c>
@@ -7845,7 +7861,7 @@
         <v>46275.634594907409</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6">
       <c r="A247" t="s">
         <v>13</v>
       </c>
@@ -7865,7 +7881,7 @@
         <v>46286.594907407409</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6">
       <c r="A248" t="s">
         <v>13</v>
       </c>
@@ -7885,7 +7901,7 @@
         <v>46286.451504629629</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6">
       <c r="A249" t="s">
         <v>13</v>
       </c>
@@ -7905,7 +7921,7 @@
         <v>46269.266851851855</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6">
       <c r="A250" t="s">
         <v>13</v>
       </c>
@@ -7925,7 +7941,7 @@
         <v>46266.560023148151</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6">
       <c r="A251" t="s">
         <v>13</v>
       </c>
@@ -7945,7 +7961,7 @@
         <v>46224.252928240741</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6">
       <c r="A252" t="s">
         <v>13</v>
       </c>
@@ -7965,7 +7981,7 @@
         <v>46267.72383101852</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6">
       <c r="A253" t="s">
         <v>13</v>
       </c>
@@ -7985,7 +8001,7 @@
         <v>46283.586840277778</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6">
       <c r="A254" t="s">
         <v>13</v>
       </c>
@@ -8005,7 +8021,7 @@
         <v>46286.586261574077</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6">
       <c r="A255" t="s">
         <v>13</v>
       </c>
@@ -8025,7 +8041,7 @@
         <v>46275.26829861111</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6">
       <c r="A256" t="s">
         <v>13</v>
       </c>
@@ -8045,7 +8061,7 @@
         <v>46260.129166666666</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6">
       <c r="A257" t="s">
         <v>13</v>
       </c>
@@ -8065,7 +8081,7 @@
         <v>46243.020405092589</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6">
       <c r="A258" t="s">
         <v>13</v>
       </c>
@@ -8085,7 +8101,7 @@
         <v>46267.27752314815</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6">
       <c r="A259" t="s">
         <v>13</v>
       </c>
@@ -8105,7 +8121,7 @@
         <v>46271.264027777775</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6">
       <c r="A260" t="s">
         <v>13</v>
       </c>
@@ -8125,7 +8141,7 @@
         <v>46155.99113425926</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6">
       <c r="A261" t="s">
         <v>13</v>
       </c>
@@ -8145,7 +8161,7 @@
         <v>46218.267881944441</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6">
       <c r="A262" t="s">
         <v>13</v>
       </c>
@@ -8165,7 +8181,7 @@
         <v>46146.26457175926</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6">
       <c r="A263" t="s">
         <v>13</v>
       </c>
@@ -8185,7 +8201,7 @@
         <v>46212.592291666668</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6">
       <c r="A264" t="s">
         <v>13</v>
       </c>
@@ -8205,7 +8221,7 @@
         <v>46248.098946759259</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6">
       <c r="A265" t="s">
         <v>13</v>
       </c>
@@ -8225,7 +8241,7 @@
         <v>46275.773414351854</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6">
       <c r="A266" t="s">
         <v>13</v>
       </c>
@@ -8245,7 +8261,7 @@
         <v>46275.773229166669</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6">
       <c r="A267" t="s">
         <v>13</v>
       </c>
@@ -8265,7 +8281,7 @@
         <v>46275.773506944446</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6">
       <c r="A268" t="s">
         <v>13</v>
       </c>
@@ -8285,7 +8301,7 @@
         <v>46275.771111111113</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6">
       <c r="A269" t="s">
         <v>13</v>
       </c>
@@ -8305,7 +8321,7 @@
         <v>46199.576053240744</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6">
       <c r="A270" t="s">
         <v>13</v>
       </c>
@@ -8325,7 +8341,7 @@
         <v>46285.896736111114</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6">
       <c r="A271" t="s">
         <v>13</v>
       </c>
@@ -8345,7 +8361,7 @@
         <v>46275.773368055554</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6">
       <c r="A272" t="s">
         <v>13</v>
       </c>
@@ -8365,7 +8381,7 @@
         <v>46275.773402777777</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6">
       <c r="A273" t="s">
         <v>13</v>
       </c>
@@ -8385,7 +8401,7 @@
         <v>46275.7734837963</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6">
       <c r="A274" t="s">
         <v>13</v>
       </c>
@@ -8405,7 +8421,7 @@
         <v>46286.951423611114</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6">
       <c r="A275" t="s">
         <v>13</v>
       </c>
@@ -8425,7 +8441,7 @@
         <v>46275.772951388892</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6">
       <c r="A276" t="s">
         <v>13</v>
       </c>
@@ -8445,7 +8461,7 @@
         <v>46274.450381944444</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6">
       <c r="A277" t="s">
         <v>13</v>
       </c>
@@ -8465,7 +8481,7 @@
         <v>46275.773321759261</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6">
       <c r="A278" t="s">
         <v>13</v>
       </c>
@@ -8485,7 +8501,7 @@
         <v>46280.594282407408</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6">
       <c r="A279" t="s">
         <v>13</v>
       </c>
@@ -8505,7 +8521,7 @@
         <v>46215.708124999997</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6">
       <c r="A280" t="s">
         <v>13</v>
       </c>
@@ -8525,7 +8541,7 @@
         <v>46275.773472222223</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6">
       <c r="A281" t="s">
         <v>13</v>
       </c>
@@ -8545,7 +8561,7 @@
         <v>46275.773229166669</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6">
       <c r="A282" t="s">
         <v>13</v>
       </c>
@@ -8565,7 +8581,7 @@
         <v>46275.773495370369</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6">
       <c r="A283" t="s">
         <v>13</v>
       </c>
@@ -8585,7 +8601,7 @@
         <v>46275.773414351854</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6">
       <c r="A284" t="s">
         <v>13</v>
       </c>
@@ -8605,7 +8621,7 @@
         <v>46286.882604166669</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6">
       <c r="A285" t="s">
         <v>13</v>
       </c>
@@ -8625,7 +8641,7 @@
         <v>46275.7733912037</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6">
       <c r="A286" t="s">
         <v>13</v>
       </c>
@@ -8645,7 +8661,7 @@
         <v>46206.03020833333</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6">
       <c r="A287" t="s">
         <v>13</v>
       </c>
@@ -8665,7 +8681,7 @@
         <v>46286.996331018519</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6">
       <c r="A288" t="s">
         <v>13</v>
       </c>
@@ -8685,7 +8701,7 @@
         <v>46275.773263888892</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6">
       <c r="A289" t="s">
         <v>13</v>
       </c>
@@ -8705,7 +8721,7 @@
         <v>46281.766296296293</v>
       </c>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:6">
       <c r="A290" t="s">
         <v>13</v>
       </c>
@@ -8725,7 +8741,7 @@
         <v>46275.773495370369</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6">
       <c r="A291" t="s">
         <v>13</v>
       </c>
@@ -8745,7 +8761,7 @@
         <v>46286.962291666663</v>
       </c>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:6">
       <c r="A292" t="s">
         <v>13</v>
       </c>
@@ -8765,7 +8781,7 @@
         <v>46275.773356481484</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6">
       <c r="A293" t="s">
         <v>272</v>
       </c>
@@ -8785,7 +8801,7 @@
         <v>46231.095625000002</v>
       </c>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:6">
       <c r="A294" t="s">
         <v>272</v>
       </c>
@@ -8805,7 +8821,7 @@
         <v>46231.092175925929</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6">
       <c r="A295" t="s">
         <v>272</v>
       </c>
@@ -8825,7 +8841,7 @@
         <v>46238.381851851853</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6">
       <c r="A296" t="s">
         <v>272</v>
       </c>
@@ -8845,7 +8861,7 @@
         <v>46238.383993055555</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6">
       <c r="A297" t="s">
         <v>272</v>
       </c>
@@ -8865,7 +8881,7 @@
         <v>46238.379687499997</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6">
       <c r="A298" t="s">
         <v>272</v>
       </c>
@@ -8885,7 +8901,7 @@
         <v>46227.09443287037</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6">
       <c r="A299" t="s">
         <v>272</v>
       </c>
@@ -8905,7 +8921,7 @@
         <v>46248.684988425928</v>
       </c>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:6">
       <c r="A300" t="s">
         <v>272</v>
       </c>
@@ -8925,7 +8941,7 @@
         <v>46238.376134259262</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6">
       <c r="A301" t="s">
         <v>272</v>
       </c>
@@ -8945,7 +8961,7 @@
         <v>46238.708854166667</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6">
       <c r="A302" t="s">
         <v>272</v>
       </c>
@@ -8965,7 +8981,7 @@
         <v>46231.032696759263</v>
       </c>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:6">
       <c r="A303" t="s">
         <v>272</v>
       </c>
@@ -8985,7 +9001,7 @@
         <v>46238.378263888888</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6">
       <c r="A304" t="s">
         <v>272</v>
       </c>
@@ -9005,7 +9021,7 @@
         <v>46238.383993055555</v>
       </c>
     </row>
-    <row r="305" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12">
       <c r="A305" t="s">
         <v>272</v>
       </c>
@@ -9025,7 +9041,7 @@
         <v>46238.381840277776</v>
       </c>
     </row>
-    <row r="306" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12">
       <c r="A306" t="s">
         <v>272</v>
       </c>
@@ -9045,7 +9061,7 @@
         <v>46248.739236111112</v>
       </c>
     </row>
-    <row r="307" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12">
       <c r="A307" t="s">
         <v>272</v>
       </c>
@@ -9065,7 +9081,7 @@
         <v>46248.692974537036</v>
       </c>
     </row>
-    <row r="308" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12">
       <c r="A308" t="s">
         <v>272</v>
       </c>
@@ -9085,7 +9101,7 @@
         <v>46270.219675925924</v>
       </c>
     </row>
-    <row r="309" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12">
       <c r="A309" t="s">
         <v>272</v>
       </c>
@@ -9105,7 +9121,7 @@
         <v>46251.317673611113</v>
       </c>
     </row>
-    <row r="310" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12">
       <c r="A310" t="s">
         <v>290</v>
       </c>
@@ -9125,7 +9141,7 @@
         <v>46286.939166666663</v>
       </c>
     </row>
-    <row r="311" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12">
       <c r="A311" t="s">
         <v>290</v>
       </c>
@@ -9145,7 +9161,7 @@
         <v>46286.98945601852</v>
       </c>
     </row>
-    <row r="312" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12">
       <c r="A312" t="s">
         <v>290</v>
       </c>
@@ -9165,18 +9181,18 @@
         <v>46286.941446759258</v>
       </c>
       <c r="J312" t="s">
-        <v>664</v>
+        <v>294</v>
       </c>
       <c r="L312" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="313" spans="1:12" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="313" spans="1:12">
       <c r="A313" t="s">
         <v>290</v>
       </c>
       <c r="B313" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C313">
         <v>3513</v>
@@ -9191,15 +9207,15 @@
         <v>46286.990231481483</v>
       </c>
       <c r="J313" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="314" spans="1:12" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12">
       <c r="A314" t="s">
         <v>290</v>
       </c>
       <c r="B314" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="C314">
         <v>3207</v>
@@ -9214,18 +9230,18 @@
         <v>46286.922465277778</v>
       </c>
       <c r="J314" t="s">
-        <v>666</v>
+        <v>299</v>
       </c>
       <c r="L314" t="s">
-        <v>673</v>
-      </c>
-    </row>
-    <row r="315" spans="1:12" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12">
       <c r="A315" t="s">
         <v>290</v>
       </c>
       <c r="B315" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C315">
         <v>1559</v>
@@ -9240,15 +9256,15 @@
         <v>46286.939293981479</v>
       </c>
       <c r="J315" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="316" spans="1:12" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12">
       <c r="A316" t="s">
         <v>290</v>
       </c>
       <c r="B316" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C316">
         <v>1353</v>
@@ -9263,15 +9279,15 @@
         <v>46286.936851851853</v>
       </c>
       <c r="J316" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="317" spans="1:12" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12">
       <c r="A317" t="s">
         <v>290</v>
       </c>
       <c r="B317" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="C317">
         <v>1018</v>
@@ -9286,15 +9302,15 @@
         <v>46286.937847222223</v>
       </c>
       <c r="J317" t="s">
-        <v>671</v>
-      </c>
-    </row>
-    <row r="318" spans="1:12" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="318" spans="1:12">
       <c r="A318" t="s">
         <v>290</v>
       </c>
       <c r="B318" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C318">
         <v>994</v>
@@ -9309,15 +9325,15 @@
         <v>46286.973124999997</v>
       </c>
       <c r="J318" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="319" spans="1:12" x14ac:dyDescent="0.25">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12">
       <c r="A319" t="s">
         <v>290</v>
       </c>
       <c r="B319" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C319">
         <v>994</v>
@@ -9332,12 +9348,12 @@
         <v>46286.937824074077</v>
       </c>
     </row>
-    <row r="320" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12">
       <c r="A320" t="s">
         <v>290</v>
       </c>
       <c r="B320" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C320">
         <v>846</v>
@@ -9352,22 +9368,22 @@
         <v>46286.919791666667</v>
       </c>
       <c r="I320" s="3" t="s">
-        <v>675</v>
+        <v>311</v>
       </c>
       <c r="J320" s="2" t="s">
-        <v>672</v>
+        <v>312</v>
       </c>
       <c r="K320" s="2"/>
       <c r="L320" s="2" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
       <c r="A321" t="s">
         <v>290</v>
       </c>
       <c r="B321" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="C321">
         <v>648</v>
@@ -9382,12 +9398,12 @@
         <v>46286.93509259259</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6">
       <c r="A322" t="s">
         <v>290</v>
       </c>
       <c r="B322" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="C322">
         <v>616</v>
@@ -9402,12 +9418,12 @@
         <v>46286.936666666668</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6">
       <c r="A323" t="s">
         <v>290</v>
       </c>
       <c r="B323" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="C323">
         <v>491</v>
@@ -9422,12 +9438,12 @@
         <v>46286.86136574074</v>
       </c>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:6">
       <c r="A324" t="s">
         <v>290</v>
       </c>
       <c r="B324" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="C324">
         <v>358</v>
@@ -9442,12 +9458,12 @@
         <v>46286.937928240739</v>
       </c>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:6">
       <c r="A325" t="s">
         <v>290</v>
       </c>
       <c r="B325" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="C325">
         <v>200</v>
@@ -9462,12 +9478,12 @@
         <v>46285.296932870369</v>
       </c>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:6">
       <c r="A326" t="s">
         <v>290</v>
       </c>
       <c r="B326" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="C326">
         <v>152</v>
@@ -9482,12 +9498,12 @@
         <v>46286.68240740741</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6">
       <c r="A327" t="s">
         <v>290</v>
       </c>
       <c r="B327" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="C327">
         <v>136</v>
@@ -9502,12 +9518,12 @@
         <v>46281.625474537039</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6">
       <c r="A328" t="s">
         <v>290</v>
       </c>
       <c r="B328" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="C328">
         <v>123</v>
@@ -9522,12 +9538,12 @@
         <v>46284.931979166664</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6">
       <c r="A329" t="s">
         <v>290</v>
       </c>
       <c r="B329" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="C329">
         <v>115</v>
@@ -9542,12 +9558,12 @@
         <v>46285.270057870373</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6">
       <c r="A330" t="s">
         <v>290</v>
       </c>
       <c r="B330" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C330">
         <v>105</v>
@@ -9562,12 +9578,12 @@
         <v>46286.691967592589</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6">
       <c r="A331" t="s">
         <v>290</v>
       </c>
       <c r="B331" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="C331">
         <v>95</v>
@@ -9582,12 +9598,12 @@
         <v>46286.613912037035</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6">
       <c r="A332" t="s">
         <v>290</v>
       </c>
       <c r="B332" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="C332">
         <v>91</v>
@@ -9602,12 +9618,12 @@
         <v>46231.575925925928</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6">
       <c r="A333" t="s">
         <v>290</v>
       </c>
       <c r="B333" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="C333">
         <v>84</v>
@@ -9622,12 +9638,12 @@
         <v>46284.328310185185</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6">
       <c r="A334" t="s">
         <v>290</v>
       </c>
       <c r="B334" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="C334">
         <v>37</v>
@@ -9642,12 +9658,12 @@
         <v>46285.189375000002</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6">
       <c r="A335" t="s">
         <v>290</v>
       </c>
       <c r="B335" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="C335">
         <v>36</v>
@@ -9662,12 +9678,12 @@
         <v>46277.556273148148</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6">
       <c r="A336" t="s">
         <v>290</v>
       </c>
       <c r="B336" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C336">
         <v>33</v>
@@ -9682,12 +9698,12 @@
         <v>46285.205914351849</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6">
       <c r="A337" t="s">
         <v>290</v>
       </c>
       <c r="B337" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="C337">
         <v>20</v>
@@ -9702,12 +9718,12 @@
         <v>46286.802928240744</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6">
       <c r="A338" t="s">
         <v>290</v>
       </c>
       <c r="B338" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C338">
         <v>18</v>
@@ -9722,12 +9738,12 @@
         <v>46270.393391203703</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6">
       <c r="A339" t="s">
         <v>290</v>
       </c>
       <c r="B339" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="C339">
         <v>11</v>
@@ -9742,12 +9758,12 @@
         <v>46279.150034722225</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6">
       <c r="A340" t="s">
         <v>290</v>
       </c>
       <c r="B340" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="C340">
         <v>7</v>
@@ -9762,12 +9778,12 @@
         <v>46284.204687500001</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6">
       <c r="A341" t="s">
         <v>290</v>
       </c>
       <c r="B341" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="C341">
         <v>4</v>
@@ -9782,12 +9798,12 @@
         <v>46271.73196759259</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6">
       <c r="A342" t="s">
         <v>290</v>
       </c>
       <c r="B342" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="C342">
         <v>2</v>
@@ -9802,12 +9818,12 @@
         <v>46217.725185185183</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6">
       <c r="A343" t="s">
         <v>290</v>
       </c>
       <c r="B343" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="C343">
         <v>2</v>
@@ -9822,12 +9838,12 @@
         <v>46275.819594907407</v>
       </c>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:6">
       <c r="A344" t="s">
         <v>290</v>
       </c>
       <c r="B344" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="C344">
         <v>2</v>
@@ -9842,12 +9858,12 @@
         <v>46227.665486111109</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6">
       <c r="A345" t="s">
         <v>290</v>
       </c>
       <c r="B345" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9862,12 +9878,12 @@
         <v>46160.90289351852</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6">
       <c r="A346" t="s">
         <v>290</v>
       </c>
       <c r="B346" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9882,12 +9898,12 @@
         <v>46160.902881944443</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B347" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="C347">
         <v>148107</v>
@@ -9902,12 +9918,12 @@
         <v>46286.93445601852</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B348" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="C348">
         <v>75998</v>
@@ -9922,12 +9938,12 @@
         <v>46286.987858796296</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B349" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="C349">
         <v>70165</v>
@@ -9942,12 +9958,12 @@
         <v>46223.629675925928</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B350" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="C350">
         <v>44747</v>
@@ -9962,12 +9978,12 @@
         <v>46286.87091435185</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B351" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C351">
         <v>38392</v>
@@ -9982,12 +9998,12 @@
         <v>46266.841747685183</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6">
       <c r="A352" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B352" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="C352">
         <v>23440</v>
@@ -10002,12 +10018,12 @@
         <v>46286.966365740744</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6">
       <c r="A353" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B353" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C353">
         <v>22347</v>
@@ -10022,12 +10038,12 @@
         <v>46223.620115740741</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6">
       <c r="A354" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B354" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="C354">
         <v>21828</v>
@@ -10042,12 +10058,12 @@
         <v>46223.614849537036</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6">
       <c r="A355" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B355" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C355">
         <v>19358</v>
@@ -10062,12 +10078,12 @@
         <v>46223.612928240742</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6">
       <c r="A356" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B356" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C356">
         <v>19297</v>
@@ -10082,12 +10098,12 @@
         <v>46286.908136574071</v>
       </c>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:6">
       <c r="A357" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B357" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C357">
         <v>18148</v>
@@ -10102,12 +10118,12 @@
         <v>46266.602395833332</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6">
       <c r="A358" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B358" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C358">
         <v>15730</v>
@@ -10122,12 +10138,12 @@
         <v>46225.182372685187</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6">
       <c r="A359" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B359" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C359">
         <v>15443</v>
@@ -10142,12 +10158,12 @@
         <v>46223.617534722223</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6">
       <c r="A360" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B360" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="C360">
         <v>14788</v>
@@ -10162,12 +10178,12 @@
         <v>46223.626226851855</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6">
       <c r="A361" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B361" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="C361">
         <v>14458</v>
@@ -10182,12 +10198,12 @@
         <v>46223.6171412037</v>
       </c>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:6">
       <c r="A362" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B362" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="C362">
         <v>12542</v>
@@ -10202,12 +10218,12 @@
         <v>46223.625300925924</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6">
       <c r="A363" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B363" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="C363">
         <v>12304</v>
@@ -10222,12 +10238,12 @@
         <v>46285.377326388887</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6">
       <c r="A364" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B364" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C364">
         <v>12112</v>
@@ -10242,12 +10258,12 @@
         <v>46223.630208333336</v>
       </c>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:6">
       <c r="A365" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B365" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="C365">
         <v>11481</v>
@@ -10262,12 +10278,12 @@
         <v>46225.190833333334</v>
       </c>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:6">
       <c r="A366" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B366" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C366">
         <v>11346</v>
@@ -10282,12 +10298,12 @@
         <v>46286.757349537038</v>
       </c>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:6">
       <c r="A367" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B367" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="C367">
         <v>11295</v>
@@ -10302,12 +10318,12 @@
         <v>46225.186863425923</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6">
       <c r="A368" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B368" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="C368">
         <v>10822</v>
@@ -10322,12 +10338,12 @@
         <v>46225.189768518518</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6">
       <c r="A369" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B369" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="C369">
         <v>10248</v>
@@ -10342,12 +10358,12 @@
         <v>46223.618321759262</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6">
       <c r="A370" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B370" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="C370">
         <v>9816</v>
@@ -10362,12 +10378,12 @@
         <v>46223.627337962964</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6">
       <c r="A371" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B371" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C371">
         <v>9720</v>
@@ -10382,12 +10398,12 @@
         <v>46225.189004629632</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6">
       <c r="A372" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B372" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="C372">
         <v>9670</v>
@@ -10402,12 +10418,12 @@
         <v>46225.195451388892</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6">
       <c r="A373" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B373" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C373">
         <v>9468</v>
@@ -10422,12 +10438,12 @@
         <v>46286.804293981484</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6">
       <c r="A374" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B374" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="C374">
         <v>8836</v>
@@ -10442,12 +10458,12 @@
         <v>46182.21166666667</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6">
       <c r="A375" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B375" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C375">
         <v>8830</v>
@@ -10462,12 +10478,12 @@
         <v>46286.869050925925</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6">
       <c r="A376" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B376" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C376">
         <v>8263</v>
@@ -10482,12 +10498,12 @@
         <v>46223.610729166663</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6">
       <c r="A377" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B377" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="C377">
         <v>8081</v>
@@ -10502,12 +10518,12 @@
         <v>46223.613807870373</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6">
       <c r="A378" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B378" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="C378">
         <v>8035</v>
@@ -10522,12 +10538,12 @@
         <v>46225.191736111112</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6">
       <c r="A379" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B379" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="C379">
         <v>7808</v>
@@ -10542,12 +10558,12 @@
         <v>46225.187858796293</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6">
       <c r="A380" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B380" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="C380">
         <v>7797</v>
@@ -10562,12 +10578,12 @@
         <v>46225.153715277775</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6">
       <c r="A381" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B381" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C381">
         <v>7657</v>
@@ -10582,12 +10598,12 @@
         <v>46223.635057870371</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6">
       <c r="A382" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B382" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="C382">
         <v>7566</v>
@@ -10602,12 +10618,12 @@
         <v>46182.210138888891</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6">
       <c r="A383" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B383" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C383">
         <v>7392</v>
@@ -10622,12 +10638,12 @@
         <v>46223.633935185186</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6">
       <c r="A384" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B384" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="C384">
         <v>7385</v>
@@ -10642,12 +10658,12 @@
         <v>46225.189525462964</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6">
       <c r="A385" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B385" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C385">
         <v>7043</v>
@@ -10662,12 +10678,12 @@
         <v>46223.570173611108</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6">
       <c r="A386" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B386" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="C386">
         <v>6519</v>
@@ -10682,12 +10698,12 @@
         <v>46223.622013888889</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6">
       <c r="A387" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B387" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="C387">
         <v>6267</v>
@@ -10702,12 +10718,12 @@
         <v>46223.629502314812</v>
       </c>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:6">
       <c r="A388" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B388" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="C388">
         <v>6168</v>
@@ -10722,12 +10738,12 @@
         <v>46201.212766203702</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6">
       <c r="A389" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B389" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="C389">
         <v>5743</v>
@@ -10742,12 +10758,12 @@
         <v>46223.625104166669</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6">
       <c r="A390" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B390" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="C390">
         <v>5467</v>
@@ -10762,12 +10778,12 @@
         <v>46223.626145833332</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6">
       <c r="A391" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B391" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="C391">
         <v>5460</v>
@@ -10782,12 +10798,12 @@
         <v>46223.623726851853</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6">
       <c r="A392" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B392" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="C392">
         <v>5423</v>
@@ -10802,12 +10818,12 @@
         <v>46286.812245370369</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6">
       <c r="A393" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B393" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="C393">
         <v>5305</v>
@@ -10822,12 +10838,12 @@
         <v>46223.610925925925</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6">
       <c r="A394" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B394" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="C394">
         <v>5303</v>
@@ -10842,12 +10858,12 @@
         <v>46225.192847222221</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6">
       <c r="A395" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B395" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="C395">
         <v>4965</v>
@@ -10862,12 +10878,12 @@
         <v>46223.623865740738</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6">
       <c r="A396" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B396" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="C396">
         <v>4844</v>
@@ -10882,12 +10898,12 @@
         <v>46225.191851851851</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6">
       <c r="A397" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B397" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="C397">
         <v>4789</v>
@@ -10902,12 +10918,12 @@
         <v>46223.626851851855</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6">
       <c r="A398" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B398" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C398">
         <v>4770</v>
@@ -10922,12 +10938,12 @@
         <v>46223.629687499997</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6">
       <c r="A399" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B399" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="C399">
         <v>4730</v>
@@ -10942,12 +10958,12 @@
         <v>46223.611875000002</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6">
       <c r="A400" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B400" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="C400">
         <v>4710</v>
@@ -10962,12 +10978,12 @@
         <v>46223.6093287037</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6">
       <c r="A401" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B401" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="C401">
         <v>4445</v>
@@ -10982,12 +10998,12 @@
         <v>46223.622511574074</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6">
       <c r="A402" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B402" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="C402">
         <v>4315</v>
@@ -11002,12 +11018,12 @@
         <v>46223.629120370373</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6">
       <c r="A403" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B403" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="C403">
         <v>4036</v>
@@ -11022,12 +11038,12 @@
         <v>46225.192129629628</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6">
       <c r="A404" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B404" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="C404">
         <v>3975</v>
@@ -11042,12 +11058,12 @@
         <v>46225.194328703707</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6">
       <c r="A405" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B405" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="C405">
         <v>3972</v>
@@ -11062,12 +11078,12 @@
         <v>46223.61347222222</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6">
       <c r="A406" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B406" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="C406">
         <v>3969</v>
@@ -11082,12 +11098,12 @@
         <v>46225.190578703703</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6">
       <c r="A407" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B407" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="C407">
         <v>3936</v>
@@ -11102,12 +11118,12 @@
         <v>46223.502164351848</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6">
       <c r="A408" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B408" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="C408">
         <v>3859</v>
@@ -11122,12 +11138,12 @@
         <v>46223.601886574077</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6">
       <c r="A409" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B409" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="C409">
         <v>3376</v>
@@ -11142,12 +11158,12 @@
         <v>46223.602476851855</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6">
       <c r="A410" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B410" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
       <c r="C410">
         <v>3346</v>
@@ -11162,12 +11178,12 @@
         <v>46225.19599537037</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6">
       <c r="A411" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B411" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="C411">
         <v>3342</v>
@@ -11182,12 +11198,12 @@
         <v>46223.611203703702</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6">
       <c r="A412" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B412" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
       <c r="C412">
         <v>3330</v>
@@ -11202,12 +11218,12 @@
         <v>46223.616168981483</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6">
       <c r="A413" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B413" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="C413">
         <v>3330</v>
@@ -11222,12 +11238,12 @@
         <v>46225.195324074077</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6">
       <c r="A414" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B414" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="C414">
         <v>3289</v>
@@ -11242,12 +11258,12 @@
         <v>46223.62940972222</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6">
       <c r="A415" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B415" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
       <c r="C415">
         <v>3278</v>
@@ -11262,12 +11278,12 @@
         <v>46225.186249999999</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6">
       <c r="A416" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B416" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="C416">
         <v>2958</v>
@@ -11282,12 +11298,12 @@
         <v>46223.58357638889</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6">
       <c r="A417" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B417" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="C417">
         <v>2946</v>
@@ -11302,12 +11318,12 @@
         <v>46223.621550925927</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6">
       <c r="A418" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B418" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="C418">
         <v>2913</v>
@@ -11322,12 +11338,12 @@
         <v>46223.624513888892</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6">
       <c r="A419" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B419" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="C419">
         <v>2859</v>
@@ -11342,12 +11358,12 @@
         <v>46223.341562499998</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6">
       <c r="A420" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B420" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C420">
         <v>2844</v>
@@ -11362,12 +11378,12 @@
         <v>46223.6253125</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6">
       <c r="A421" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B421" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
       <c r="C421">
         <v>2822</v>
@@ -11382,12 +11398,12 @@
         <v>46223.583831018521</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6">
       <c r="A422" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B422" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="C422">
         <v>2759</v>
@@ -11402,12 +11418,12 @@
         <v>46223.6090625</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6">
       <c r="A423" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B423" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
       <c r="C423">
         <v>2753</v>
@@ -11422,12 +11438,12 @@
         <v>46225.1875</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6">
       <c r="A424" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B424" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C424">
         <v>2691</v>
@@ -11442,12 +11458,12 @@
         <v>46222.871805555558</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6">
       <c r="A425" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B425" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="C425">
         <v>2690</v>
@@ -11462,12 +11478,12 @@
         <v>46223.60728009259</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6">
       <c r="A426" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B426" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="C426">
         <v>2643</v>
@@ -11482,12 +11498,12 @@
         <v>46223.198657407411</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6">
       <c r="A427" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B427" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="C427">
         <v>2630</v>
@@ -11502,12 +11518,12 @@
         <v>46223.622743055559</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6">
       <c r="A428" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B428" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="C428">
         <v>2567</v>
@@ -11522,12 +11538,12 @@
         <v>46286.185636574075</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6">
       <c r="A429" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B429" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="C429">
         <v>2492</v>
@@ -11542,12 +11558,12 @@
         <v>46223.596990740742</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6">
       <c r="A430" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B430" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="C430">
         <v>2427</v>
@@ -11562,12 +11578,12 @@
         <v>46223.63144675926</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6">
       <c r="A431" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B431" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C431">
         <v>2370</v>
@@ -11582,12 +11598,12 @@
         <v>46225.183842592596</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6">
       <c r="A432" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B432" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="C432">
         <v>2285</v>
@@ -11602,12 +11618,12 @@
         <v>46225.185300925928</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6">
       <c r="A433" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B433" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="C433">
         <v>2207</v>
@@ -11622,12 +11638,12 @@
         <v>46223.547766203701</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6">
       <c r="A434" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B434" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="C434">
         <v>2168</v>
@@ -11642,12 +11658,12 @@
         <v>46225.192245370374</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6">
       <c r="A435" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B435" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C435">
         <v>2166</v>
@@ -11662,12 +11678,12 @@
         <v>46222.254525462966</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6">
       <c r="A436" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B436" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="C436">
         <v>2102</v>
@@ -11682,12 +11698,12 @@
         <v>46223.593148148146</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6">
       <c r="A437" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B437" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C437">
         <v>2084</v>
@@ -11702,12 +11718,12 @@
         <v>46223.634155092594</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6">
       <c r="A438" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B438" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="C438">
         <v>2056</v>
@@ -11722,12 +11738,12 @@
         <v>46172.275405092594</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6">
       <c r="A439" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B439" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="C439">
         <v>2056</v>
@@ -11742,12 +11758,12 @@
         <v>46225.192048611112</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6">
       <c r="A440" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B440" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="C440">
         <v>2047</v>
@@ -11762,12 +11778,12 @@
         <v>46225.193495370368</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6">
       <c r="A441" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B441" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="C441">
         <v>2045</v>
@@ -11782,12 +11798,12 @@
         <v>46223.61478009259</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6">
       <c r="A442" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B442" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="C442">
         <v>2025</v>
@@ -11802,12 +11818,12 @@
         <v>46223.620567129627</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6">
       <c r="A443" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B443" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="C443">
         <v>2004</v>
@@ -11822,12 +11838,12 @@
         <v>46223.609039351853</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6">
       <c r="A444" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B444" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C444">
         <v>1939</v>
@@ -11842,12 +11858,12 @@
         <v>46223.59888888889</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6">
       <c r="A445" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B445" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="C445">
         <v>1885</v>
@@ -11862,12 +11878,12 @@
         <v>46222.255798611113</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6">
       <c r="A446" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B446" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="C446">
         <v>1877</v>
@@ -11882,12 +11898,12 @@
         <v>46223.620347222219</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6">
       <c r="A447" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B447" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="C447">
         <v>1863</v>
@@ -11902,12 +11918,12 @@
         <v>46223.627118055556</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6">
       <c r="A448" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B448" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="C448">
         <v>1847</v>
@@ -11922,12 +11938,12 @@
         <v>46225.190821759257</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6">
       <c r="A449" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B449" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C449">
         <v>1826</v>
@@ -11942,12 +11958,12 @@
         <v>46223.544050925928</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6">
       <c r="A450" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B450" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="C450">
         <v>1817</v>
@@ -11962,12 +11978,12 @@
         <v>46222.21471064815</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6">
       <c r="A451" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B451" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="C451">
         <v>1811</v>
@@ -11982,12 +11998,12 @@
         <v>46222.820717592593</v>
       </c>
     </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:6">
       <c r="A452" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B452" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="C452">
         <v>1747</v>
@@ -12002,12 +12018,12 @@
         <v>46223.614664351851</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6">
       <c r="A453" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B453" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C453">
         <v>1729</v>
@@ -12022,12 +12038,12 @@
         <v>46223.563240740739</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6">
       <c r="A454" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B454" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="C454">
         <v>1728</v>
@@ -12042,12 +12058,12 @@
         <v>46223.567928240744</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6">
       <c r="A455" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B455" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="C455">
         <v>1715</v>
@@ -12062,12 +12078,12 @@
         <v>46224.865439814814</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6">
       <c r="A456" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B456" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="C456">
         <v>1688</v>
@@ -12082,12 +12098,12 @@
         <v>46224.834456018521</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6">
       <c r="A457" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B457" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="C457">
         <v>1683</v>
@@ -12102,12 +12118,12 @@
         <v>46223.608773148146</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6">
       <c r="A458" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B458" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="C458">
         <v>1673</v>
@@ -12122,12 +12138,12 @@
         <v>46223.620497685188</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6">
       <c r="A459" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B459" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="C459">
         <v>1662</v>
@@ -12142,12 +12158,12 @@
         <v>46223.621886574074</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6">
       <c r="A460" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B460" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="C460">
         <v>1657</v>
@@ -12162,12 +12178,12 @@
         <v>46223.258680555555</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6">
       <c r="A461" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B461" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="C461">
         <v>1588</v>
@@ -12182,12 +12198,12 @@
         <v>46223.613553240742</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6">
       <c r="A462" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B462" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C462">
         <v>1586</v>
@@ -12202,12 +12218,12 @@
         <v>46223.582141203704</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6">
       <c r="A463" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B463" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C463">
         <v>1576</v>
@@ -12222,12 +12238,12 @@
         <v>46223.619953703703</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6">
       <c r="A464" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B464" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C464">
         <v>1557</v>
@@ -12242,12 +12258,12 @@
         <v>46223.606469907405</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6">
       <c r="A465" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B465" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="C465">
         <v>1556</v>
@@ -12262,12 +12278,12 @@
         <v>46223.614687499998</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6">
       <c r="A466" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B466" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="C466">
         <v>1551</v>
@@ -12282,12 +12298,12 @@
         <v>46223.634143518517</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6">
       <c r="A467" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B467" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="C467">
         <v>1515</v>
@@ -12302,12 +12318,12 @@
         <v>46225.187395833331</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6">
       <c r="A468" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B468" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="C468">
         <v>1514</v>
@@ -12322,12 +12338,12 @@
         <v>46223.621944444443</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6">
       <c r="A469" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B469" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C469">
         <v>1505</v>
@@ -12342,12 +12358,12 @@
         <v>46223.605000000003</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6">
       <c r="A470" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B470" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="C470">
         <v>1463</v>
@@ -12362,12 +12378,12 @@
         <v>46223.630162037036</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6">
       <c r="A471" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B471" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="C471">
         <v>1444</v>
@@ -12382,12 +12398,12 @@
         <v>46225.193622685183</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6">
       <c r="A472" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B472" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="C472">
         <v>1433</v>
@@ -12402,12 +12418,12 @@
         <v>46223.617766203701</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6">
       <c r="A473" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B473" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="C473">
         <v>1420</v>
@@ -12422,12 +12438,12 @@
         <v>46223.116562499999</v>
       </c>
     </row>
-    <row r="474" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:6">
       <c r="A474" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B474" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="C474">
         <v>1332</v>
@@ -12442,12 +12458,12 @@
         <v>46223.596516203703</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6">
       <c r="A475" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B475" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C475">
         <v>1306</v>
@@ -12462,12 +12478,12 @@
         <v>46222.699155092596</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6">
       <c r="A476" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B476" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C476">
         <v>1269</v>
@@ -12482,12 +12498,12 @@
         <v>46223.609375</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6">
       <c r="A477" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B477" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="C477">
         <v>1261</v>
@@ -12502,12 +12518,12 @@
         <v>46225.185624999998</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6">
       <c r="A478" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B478" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="C478">
         <v>1247</v>
@@ -12522,12 +12538,12 @@
         <v>46222.257731481484</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6">
       <c r="A479" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B479" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C479">
         <v>1242</v>
@@ -12542,12 +12558,12 @@
         <v>46223.622037037036</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6">
       <c r="A480" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B480" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="C480">
         <v>1206</v>
@@ -12562,12 +12578,12 @@
         <v>46222.256157407406</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6">
       <c r="A481" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B481" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="C481">
         <v>1204</v>
@@ -12582,12 +12598,12 @@
         <v>46222.254884259259</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6">
       <c r="A482" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B482" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="C482">
         <v>1120</v>
@@ -12602,12 +12618,12 @@
         <v>46286.77679398148</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6">
       <c r="A483" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B483" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="C483">
         <v>1120</v>
@@ -12622,12 +12638,12 @@
         <v>46222.879918981482</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6">
       <c r="A484" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B484" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="C484">
         <v>1113</v>
@@ -12642,12 +12658,12 @@
         <v>46225.182500000003</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6">
       <c r="A485" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B485" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="C485">
         <v>1110</v>
@@ -12662,12 +12678,12 @@
         <v>46223.622835648152</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6">
       <c r="A486" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B486" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="C486">
         <v>1071</v>
@@ -12682,12 +12698,12 @@
         <v>46223.630300925928</v>
       </c>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:6">
       <c r="A487" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B487" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="C487">
         <v>1059</v>
@@ -12702,12 +12718,12 @@
         <v>46223.608877314815</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6">
       <c r="A488" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B488" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="C488">
         <v>1039</v>
@@ -12722,12 +12738,12 @@
         <v>46223.617777777778</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6">
       <c r="A489" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B489" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="C489">
         <v>1036</v>
@@ -12742,12 +12758,12 @@
         <v>46223.579872685186</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6">
       <c r="A490" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B490" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="C490">
         <v>1035</v>
@@ -12762,12 +12778,12 @@
         <v>46224.736180555556</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6">
       <c r="A491" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B491" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="C491">
         <v>1021</v>
@@ -12782,12 +12798,12 @@
         <v>46223.625185185185</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6">
       <c r="A492" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B492" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="C492">
         <v>996</v>
@@ -12802,12 +12818,12 @@
         <v>46223.608113425929</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6">
       <c r="A493" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B493" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="C493">
         <v>987</v>
@@ -12822,12 +12838,12 @@
         <v>46223.626770833333</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6">
       <c r="A494" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B494" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="C494">
         <v>980</v>
@@ -12842,12 +12858,12 @@
         <v>46222.78429398148</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6">
       <c r="A495" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B495" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C495">
         <v>970</v>
@@ -12862,12 +12878,12 @@
         <v>46221.9922337963</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6">
       <c r="A496" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B496" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="C496">
         <v>969</v>
@@ -12882,12 +12898,12 @@
         <v>46222.256307870368</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6">
       <c r="A497" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B497" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="C497">
         <v>967</v>
@@ -12902,12 +12918,12 @@
         <v>46224.654780092591</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6">
       <c r="A498" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B498" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="C498">
         <v>958</v>
@@ -12922,12 +12938,12 @@
         <v>46219.194710648146</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6">
       <c r="A499" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B499" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="C499">
         <v>955</v>
@@ -12942,12 +12958,12 @@
         <v>46223.624965277777</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6">
       <c r="A500" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B500" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="C500">
         <v>944</v>
@@ -12962,12 +12978,12 @@
         <v>46223.615752314814</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6">
       <c r="A501" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B501" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="C501">
         <v>908</v>
@@ -12982,12 +12998,12 @@
         <v>46223.536192129628</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6">
       <c r="A502" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B502" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="C502">
         <v>905</v>
@@ -13002,12 +13018,12 @@
         <v>46223.60083333333</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6">
       <c r="A503" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B503" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="C503">
         <v>898</v>
@@ -13022,12 +13038,12 @@
         <v>46222.255011574074</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6">
       <c r="A504" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B504" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="C504">
         <v>878</v>
@@ -13042,12 +13058,12 @@
         <v>46223.613877314812</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6">
       <c r="A505" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B505" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="C505">
         <v>875</v>
@@ -13062,12 +13078,12 @@
         <v>46222.791134259256</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6">
       <c r="A506" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B506" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="C506">
         <v>861</v>
@@ -13082,12 +13098,12 @@
         <v>46225.185798611114</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6">
       <c r="A507" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B507" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="C507">
         <v>844</v>
@@ -13102,12 +13118,12 @@
         <v>46222.255347222221</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6">
       <c r="A508" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B508" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="C508">
         <v>843</v>
@@ -13122,12 +13138,12 @@
         <v>46173.262685185182</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6">
       <c r="A509" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B509" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
       <c r="C509">
         <v>827</v>
@@ -13142,12 +13158,12 @@
         <v>46225.17224537037</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6">
       <c r="A510" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B510" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="C510">
         <v>811</v>
@@ -13162,12 +13178,12 @@
         <v>46225.184270833335</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6">
       <c r="A511" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B511" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="C511">
         <v>802</v>
@@ -13182,12 +13198,12 @@
         <v>46222.256215277775</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6">
       <c r="A512" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B512" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="C512">
         <v>798</v>
@@ -13202,12 +13218,12 @@
         <v>46222.254467592589</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6">
       <c r="A513" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B513" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="C513">
         <v>797</v>
@@ -13222,12 +13238,12 @@
         <v>46223.595983796295</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6">
       <c r="A514" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B514" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="C514">
         <v>796</v>
@@ -13242,12 +13258,12 @@
         <v>46223.626608796294</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6">
       <c r="A515" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B515" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="C515">
         <v>791</v>
@@ -13262,12 +13278,12 @@
         <v>46223.567789351851</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6">
       <c r="A516" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B516" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
       <c r="C516">
         <v>790</v>
@@ -13282,12 +13298,12 @@
         <v>46225.186469907407</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6">
       <c r="A517" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B517" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="C517">
         <v>781</v>
@@ -13302,12 +13318,12 @@
         <v>46218.255590277775</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6">
       <c r="A518" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B518" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="C518">
         <v>761</v>
@@ -13322,12 +13338,12 @@
         <v>46223.629942129628</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6">
       <c r="A519" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B519" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="C519">
         <v>740</v>
@@ -13342,12 +13358,12 @@
         <v>46223.634120370371</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6">
       <c r="A520" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B520" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="C520">
         <v>735</v>
@@ -13362,12 +13378,12 @@
         <v>46223.51829861111</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6">
       <c r="A521" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B521" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="C521">
         <v>731</v>
@@ -13382,12 +13398,12 @@
         <v>46223.554363425923</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6">
       <c r="A522" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B522" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="C522">
         <v>725</v>
@@ -13402,12 +13418,12 @@
         <v>46223.581967592596</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6">
       <c r="A523" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B523" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="C523">
         <v>707</v>
@@ -13422,12 +13438,12 @@
         <v>46223.099224537036</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6">
       <c r="A524" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B524" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="C524">
         <v>702</v>
@@ -13442,12 +13458,12 @@
         <v>46225.154189814813</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6">
       <c r="A525" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B525" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="C525">
         <v>697</v>
@@ -13462,12 +13478,12 @@
         <v>46222.896851851852</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6">
       <c r="A526" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B526" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="C526">
         <v>688</v>
@@ -13482,12 +13498,12 @@
         <v>46223.550347222219</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6">
       <c r="A527" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B527" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="C527">
         <v>684</v>
@@ -13502,12 +13518,12 @@
         <v>46223.603368055556</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6">
       <c r="A528" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B528" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="C528">
         <v>683</v>
@@ -13522,12 +13538,12 @@
         <v>46222.837175925924</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6">
       <c r="A529" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B529" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C529">
         <v>648</v>
@@ -13542,12 +13558,12 @@
         <v>46219.190717592595</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6">
       <c r="A530" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B530" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C530">
         <v>635</v>
@@ -13562,12 +13578,12 @@
         <v>46223.525543981479</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6">
       <c r="A531" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B531" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="C531">
         <v>628</v>
@@ -13582,12 +13598,12 @@
         <v>46225.174074074072</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6">
       <c r="A532" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B532" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C532">
         <v>623</v>
@@ -13602,12 +13618,12 @@
         <v>46223.616574074076</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6">
       <c r="A533" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B533" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C533">
         <v>616</v>
@@ -13622,12 +13638,12 @@
         <v>46223.629664351851</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6">
       <c r="A534" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B534" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C534">
         <v>614</v>
@@ -13642,12 +13658,12 @@
         <v>46222.93377314815</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6">
       <c r="A535" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B535" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="C535">
         <v>596</v>
@@ -13662,12 +13678,12 @@
         <v>46224.241608796299</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6">
       <c r="A536" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B536" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="C536">
         <v>579</v>
@@ -13682,12 +13698,12 @@
         <v>46225.194085648145</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6">
       <c r="A537" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B537" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="C537">
         <v>579</v>
@@ -13702,12 +13718,12 @@
         <v>46225.188252314816</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6">
       <c r="A538" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B538" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="C538">
         <v>565</v>
@@ -13722,12 +13738,12 @@
         <v>46225.152789351851</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6">
       <c r="A539" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B539" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="C539">
         <v>563</v>
@@ -13742,12 +13758,12 @@
         <v>46222.893414351849</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6">
       <c r="A540" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B540" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="C540">
         <v>557</v>
@@ -13762,12 +13778,12 @@
         <v>46223.549756944441</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6">
       <c r="A541" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B541" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="C541">
         <v>538</v>
@@ -13782,12 +13798,12 @@
         <v>46222.24827546296</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6">
       <c r="A542" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B542" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C542">
         <v>523</v>
@@ -13802,12 +13818,12 @@
         <v>46224.765277777777</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6">
       <c r="A543" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B543" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="C543">
         <v>497</v>
@@ -13822,12 +13838,12 @@
         <v>46222.915347222224</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6">
       <c r="A544" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B544" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="C544">
         <v>489</v>
@@ -13842,12 +13858,12 @@
         <v>46222.249537037038</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6">
       <c r="A545" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B545" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="C545">
         <v>461</v>
@@ -13862,12 +13878,12 @@
         <v>46222.922812500001</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6">
       <c r="A546" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B546" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="C546">
         <v>448</v>
@@ -13882,12 +13898,12 @@
         <v>46266.714479166665</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6">
       <c r="A547" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B547" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="C547">
         <v>368</v>
@@ -13902,12 +13918,12 @@
         <v>46223.63449074074</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6">
       <c r="A548" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B548" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="C548">
         <v>367</v>
@@ -13922,12 +13938,12 @@
         <v>46222.813935185186</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6">
       <c r="A549" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B549" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="C549">
         <v>363</v>
@@ -13942,12 +13958,12 @@
         <v>46222.786643518521</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6">
       <c r="A550" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B550" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="C550">
         <v>356</v>
@@ -13962,12 +13978,12 @@
         <v>46219.608356481483</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6">
       <c r="A551" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B551" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="C551">
         <v>346</v>
@@ -13982,12 +13998,12 @@
         <v>46222.870300925926</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6">
       <c r="A552" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B552" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C552">
         <v>346</v>
@@ -14002,12 +14018,12 @@
         <v>46222.688217592593</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6">
       <c r="A553" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B553" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="C553">
         <v>326</v>
@@ -14022,12 +14038,12 @@
         <v>46222.775196759256</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6">
       <c r="A554" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B554" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="C554">
         <v>319</v>
@@ -14042,12 +14058,12 @@
         <v>46223.198634259257</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6">
       <c r="A555" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B555" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="C555">
         <v>313</v>
@@ -14062,12 +14078,12 @@
         <v>46222.255358796298</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6">
       <c r="A556" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B556" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="C556">
         <v>303</v>
@@ -14082,12 +14098,12 @@
         <v>46173.261643518519</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6">
       <c r="A557" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B557" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="C557">
         <v>302</v>
@@ -14102,12 +14118,12 @@
         <v>46223.589155092595</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6">
       <c r="A558" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B558" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="C558">
         <v>300</v>
@@ -14122,12 +14138,12 @@
         <v>46223.57571759259</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6">
       <c r="A559" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B559" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="C559">
         <v>278</v>
@@ -14142,12 +14158,12 @@
         <v>46225.178020833337</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6">
       <c r="A560" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B560" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="C560">
         <v>265</v>
@@ -14162,12 +14178,12 @@
         <v>46197.996388888889</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6">
       <c r="A561" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B561" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C561">
         <v>264</v>
@@ -14182,12 +14198,12 @@
         <v>46217.250914351855</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6">
       <c r="A562" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B562" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C562">
         <v>256</v>
@@ -14202,12 +14218,12 @@
         <v>46220.693749999999</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6">
       <c r="A563" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B563" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C563">
         <v>250</v>
@@ -14222,12 +14238,12 @@
         <v>46222.686631944445</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6">
       <c r="A564" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B564" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="C564">
         <v>248</v>
@@ -14242,12 +14258,12 @@
         <v>46198.79383101852</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6">
       <c r="A565" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B565" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="C565">
         <v>244</v>
@@ -14262,12 +14278,12 @@
         <v>46223.61005787037</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6">
       <c r="A566" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B566" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="C566">
         <v>243</v>
@@ -14282,12 +14298,12 @@
         <v>46223.631782407407</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6">
       <c r="A567" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B567" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="C567">
         <v>238</v>
@@ -14302,12 +14318,12 @@
         <v>46222.833587962959</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6">
       <c r="A568" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B568" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="C568">
         <v>237</v>
@@ -14322,12 +14338,12 @@
         <v>46222.250300925924</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6">
       <c r="A569" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B569" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="C569">
         <v>235</v>
@@ -14342,12 +14358,12 @@
         <v>46225.192430555559</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6">
       <c r="A570" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B570" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="C570">
         <v>224</v>
@@ -14362,12 +14378,12 @@
         <v>46221.452743055554</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6">
       <c r="A571" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B571" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="C571">
         <v>220</v>
@@ -14382,12 +14398,12 @@
         <v>46222.255277777775</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6">
       <c r="A572" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B572" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="C572">
         <v>209</v>
@@ -14402,12 +14418,12 @@
         <v>46172.264849537038</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6">
       <c r="A573" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B573" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="C573">
         <v>208</v>
@@ -14422,12 +14438,12 @@
         <v>46172.272928240738</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6">
       <c r="A574" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B574" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="C574">
         <v>200</v>
@@ -14442,12 +14458,12 @@
         <v>46225.185231481482</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6">
       <c r="A575" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B575" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C575">
         <v>199</v>
@@ -14462,12 +14478,12 @@
         <v>46218.98300925926</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6">
       <c r="A576" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B576" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="C576">
         <v>198</v>
@@ -14482,12 +14498,12 @@
         <v>46192.54478009259</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6">
       <c r="A577" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B577" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="C577">
         <v>195</v>
@@ -14502,12 +14518,12 @@
         <v>46223.540636574071</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6">
       <c r="A578" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B578" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C578">
         <v>188</v>
@@ -14522,12 +14538,12 @@
         <v>46205.250405092593</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6">
       <c r="A579" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B579" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="C579">
         <v>183</v>
@@ -14542,12 +14558,12 @@
         <v>46192.977465277778</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6">
       <c r="A580" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B580" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="C580">
         <v>172</v>
@@ -14562,12 +14578,12 @@
         <v>46220.611678240741</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6">
       <c r="A581" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B581" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="C581">
         <v>171</v>
@@ -14582,12 +14598,12 @@
         <v>46225.165532407409</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6">
       <c r="A582" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B582" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="C582">
         <v>167</v>
@@ -14602,12 +14618,12 @@
         <v>46192.97111111111</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6">
       <c r="A583" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B583" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="C583">
         <v>163</v>
@@ -14622,12 +14638,12 @@
         <v>46223.567280092589</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6">
       <c r="A584" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B584" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="C584">
         <v>161</v>
@@ -14642,12 +14658,12 @@
         <v>46221.891284722224</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6">
       <c r="A585" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B585" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="C585">
         <v>158</v>
@@ -14662,12 +14678,12 @@
         <v>46200.350011574075</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6">
       <c r="A586" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B586" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
       <c r="C586">
         <v>156</v>
@@ -14682,12 +14698,12 @@
         <v>46222.25072916667</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6">
       <c r="A587" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B587" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="C587">
         <v>155</v>
@@ -14702,12 +14718,12 @@
         <v>46223.854270833333</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6">
       <c r="A588" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B588" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="C588">
         <v>153</v>
@@ -14722,12 +14738,12 @@
         <v>46223.115300925929</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6">
       <c r="A589" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B589" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="C589">
         <v>151</v>
@@ -14742,12 +14758,12 @@
         <v>46224.884120370371</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6">
       <c r="A590" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B590" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="C590">
         <v>147</v>
@@ -14762,12 +14778,12 @@
         <v>46224.244629629633</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6">
       <c r="A591" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B591" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="C591">
         <v>144</v>
@@ -14782,12 +14798,12 @@
         <v>46222.674560185187</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6">
       <c r="A592" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B592" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="C592">
         <v>144</v>
@@ -14802,12 +14818,12 @@
         <v>46225.178449074076</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6">
       <c r="A593" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B593" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="C593">
         <v>143</v>
@@ -14822,12 +14838,12 @@
         <v>46223.603148148148</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6">
       <c r="A594" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B594" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
       <c r="C594">
         <v>137</v>
@@ -14842,12 +14858,12 @@
         <v>46222.745312500003</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6">
       <c r="A595" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B595" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="C595">
         <v>137</v>
@@ -14862,12 +14878,12 @@
         <v>46173.262708333335</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6">
       <c r="A596" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B596" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="C596">
         <v>122</v>
@@ -14882,12 +14898,12 @@
         <v>46222.922175925924</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6">
       <c r="A597" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B597" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="C597">
         <v>113</v>
@@ -14902,12 +14918,12 @@
         <v>46172.271018518521</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6">
       <c r="A598" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B598" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C598">
         <v>109</v>
@@ -14922,12 +14938,12 @@
         <v>46203.524074074077</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6">
       <c r="A599" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B599" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="C599">
         <v>107</v>
@@ -14942,12 +14958,12 @@
         <v>46221.618738425925</v>
       </c>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:6">
       <c r="A600" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B600" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="C600">
         <v>105</v>
@@ -14962,12 +14978,12 @@
         <v>46201.526574074072</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6">
       <c r="A601" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B601" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="C601">
         <v>104</v>
@@ -14982,12 +14998,12 @@
         <v>46221.644907407404</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6">
       <c r="A602" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B602" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="C602">
         <v>104</v>
@@ -15002,12 +15018,12 @@
         <v>46221.766261574077</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6">
       <c r="A603" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B603" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
       <c r="C603">
         <v>101</v>
@@ -15022,12 +15038,12 @@
         <v>46200.624513888892</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6">
       <c r="A604" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B604" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="C604">
         <v>101</v>
@@ -15042,12 +15058,12 @@
         <v>46171.270497685182</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6">
       <c r="A605" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B605" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="C605">
         <v>98</v>
@@ -15062,12 +15078,12 @@
         <v>46173.260254629633</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6">
       <c r="A606" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B606" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="C606">
         <v>96</v>
@@ -15082,12 +15098,12 @@
         <v>46218.487870370373</v>
       </c>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:6">
       <c r="A607" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B607" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="C607">
         <v>93</v>
@@ -15102,12 +15118,12 @@
         <v>46283.66133101852</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6">
       <c r="A608" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B608" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="C608">
         <v>87</v>
@@ -15122,12 +15138,12 @@
         <v>46213.636192129627</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6">
       <c r="A609" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B609" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="C609">
         <v>84</v>
@@ -15142,12 +15158,12 @@
         <v>46173.260243055556</v>
       </c>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:6">
       <c r="A610" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B610" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="C610">
         <v>82</v>
@@ -15162,12 +15178,12 @@
         <v>46223.634525462963</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6">
       <c r="A611" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B611" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
       <c r="C611">
         <v>77</v>
@@ -15182,12 +15198,12 @@
         <v>46223.615081018521</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6">
       <c r="A612" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B612" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="C612">
         <v>77</v>
@@ -15202,12 +15218,12 @@
         <v>46222.580324074072</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6">
       <c r="A613" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B613" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="C613">
         <v>77</v>
@@ -15222,12 +15238,12 @@
         <v>46221.62128472222</v>
       </c>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:6">
       <c r="A614" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B614" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="C614">
         <v>76</v>
@@ -15242,12 +15258,12 @@
         <v>46153.784178240741</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6">
       <c r="A615" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B615" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="C615">
         <v>74</v>
@@ -15262,12 +15278,12 @@
         <v>46265.881458333337</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6">
       <c r="A616" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B616" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="C616">
         <v>70</v>
@@ -15282,12 +15298,12 @@
         <v>46203.25141203704</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6">
       <c r="A617" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B617" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="C617">
         <v>66</v>
@@ -15302,12 +15318,12 @@
         <v>46220.607476851852</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6">
       <c r="A618" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B618" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
       <c r="C618">
         <v>65</v>
@@ -15322,12 +15338,12 @@
         <v>46172.269837962966</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6">
       <c r="A619" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B619" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="C619">
         <v>64</v>
@@ -15342,12 +15358,12 @@
         <v>46222.647592592592</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6">
       <c r="A620" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B620" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="C620">
         <v>59</v>
@@ -15362,12 +15378,12 @@
         <v>46220.537395833337</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6">
       <c r="A621" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B621" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="C621">
         <v>59</v>
@@ -15382,12 +15398,12 @@
         <v>46216.698796296296</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6">
       <c r="A622" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B622" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="C622">
         <v>56</v>
@@ -15402,12 +15418,12 @@
         <v>46223.613668981481</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6">
       <c r="A623" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B623" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="C623">
         <v>55</v>
@@ -15422,12 +15438,12 @@
         <v>46173.26085648148</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6">
       <c r="A624" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B624" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="C624">
         <v>55</v>
@@ -15442,12 +15458,12 @@
         <v>46265.881377314814</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6">
       <c r="A625" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B625" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="C625">
         <v>54</v>
@@ -15462,12 +15478,12 @@
         <v>46220.604699074072</v>
       </c>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:6">
       <c r="A626" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B626" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
       <c r="C626">
         <v>51</v>
@@ -15482,12 +15498,12 @@
         <v>46222.248368055552</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6">
       <c r="A627" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B627" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="C627">
         <v>45</v>
@@ -15502,12 +15518,12 @@
         <v>46171.274942129632</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6">
       <c r="A628" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B628" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="C628">
         <v>42</v>
@@ -15522,12 +15538,12 @@
         <v>46209.78434027778</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6">
       <c r="A629" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B629" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="C629">
         <v>40</v>
@@ -15542,12 +15558,12 @@
         <v>46223.665567129632</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6">
       <c r="A630" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B630" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="C630">
         <v>38</v>
@@ -15562,12 +15578,12 @@
         <v>46225.110127314816</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6">
       <c r="A631" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B631" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="C631">
         <v>37</v>
@@ -15582,12 +15598,12 @@
         <v>46215.257361111115</v>
       </c>
     </row>
-    <row r="632" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:6">
       <c r="A632" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B632" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="C632">
         <v>36</v>
@@ -15602,12 +15618,12 @@
         <v>46286.599236111113</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6">
       <c r="A633" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B633" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="C633">
         <v>33</v>
@@ -15622,12 +15638,12 @@
         <v>46203.834930555553</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6">
       <c r="A634" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B634" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
       <c r="C634">
         <v>31</v>
@@ -15642,12 +15658,12 @@
         <v>46221.176805555559</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6">
       <c r="A635" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B635" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="C635">
         <v>30</v>
@@ -15662,12 +15678,12 @@
         <v>46209.836481481485</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6">
       <c r="A636" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B636" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="C636">
         <v>30</v>
@@ -15682,12 +15698,12 @@
         <v>46222.783310185187</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6">
       <c r="A637" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B637" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="C637">
         <v>29</v>
@@ -15702,12 +15718,12 @@
         <v>46223.650914351849</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6">
       <c r="A638" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B638" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="C638">
         <v>27</v>
@@ -15722,12 +15738,12 @@
         <v>46173.252118055556</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6">
       <c r="A639" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B639" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="C639">
         <v>27</v>
@@ -15742,12 +15758,12 @@
         <v>46182.876354166663</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6">
       <c r="A640" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B640" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="C640">
         <v>26</v>
@@ -15762,12 +15778,12 @@
         <v>46223.259097222224</v>
       </c>
     </row>
-    <row r="641" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:6">
       <c r="A641" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B641" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
       <c r="C641">
         <v>25</v>
@@ -15782,12 +15798,12 @@
         <v>46204.257060185184</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6">
       <c r="A642" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B642" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="C642">
         <v>24</v>
@@ -15802,12 +15818,12 @@
         <v>46193.02065972222</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6">
       <c r="A643" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B643" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="C643">
         <v>22</v>
@@ -15822,12 +15838,12 @@
         <v>46170.271979166668</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6">
       <c r="A644" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B644" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="C644">
         <v>20</v>
@@ -15842,12 +15858,12 @@
         <v>46192.853692129633</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6">
       <c r="A645" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B645" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="C645">
         <v>20</v>
@@ -15862,12 +15878,12 @@
         <v>46219.002916666665</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6">
       <c r="A646" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B646" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="C646">
         <v>19</v>
@@ -15882,12 +15898,12 @@
         <v>46209.732569444444</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6">
       <c r="A647" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B647" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="C647">
         <v>17</v>
@@ -15902,12 +15918,12 @@
         <v>46218.523379629631</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6">
       <c r="A648" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B648" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
       <c r="C648">
         <v>17</v>
@@ -15922,12 +15938,12 @@
         <v>46223.646655092591</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6">
       <c r="A649" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B649" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="C649">
         <v>15</v>
@@ -15942,12 +15958,12 @@
         <v>46203.860208333332</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6">
       <c r="A650" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B650" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="C650">
         <v>14</v>
@@ -15962,12 +15978,12 @@
         <v>46162.271481481483</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6">
       <c r="A651" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B651" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="C651">
         <v>13</v>
@@ -15982,12 +15998,12 @@
         <v>46178.413460648146</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6">
       <c r="A652" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B652" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="C652">
         <v>12</v>
@@ -16002,12 +16018,12 @@
         <v>46171.25677083333</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6">
       <c r="A653" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B653" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="C653">
         <v>7</v>
@@ -16022,12 +16038,12 @@
         <v>46155.576215277775</v>
       </c>
     </row>
-    <row r="654" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:6">
       <c r="A654" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B654" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="C654">
         <v>7</v>
@@ -16042,12 +16058,12 @@
         <v>46150.27443287037</v>
       </c>
     </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:6">
       <c r="A655" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B655" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
       <c r="C655">
         <v>4</v>
@@ -16062,12 +16078,12 @@
         <v>46193.28533564815</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6">
       <c r="A656" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B656" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="C656">
         <v>4</v>
@@ -16082,12 +16098,12 @@
         <v>46223.646944444445</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6">
       <c r="A657" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B657" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="C657">
         <v>4</v>
@@ -16102,12 +16118,12 @@
         <v>46219.82540509259</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6">
       <c r="A658" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B658" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="C658">
         <v>4</v>
@@ -16122,12 +16138,12 @@
         <v>46225.165312500001</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6">
       <c r="A659" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B659" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="C659">
         <v>4</v>
@@ -16142,12 +16158,12 @@
         <v>46207.258275462962</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6">
       <c r="A660" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B660" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="C660">
         <v>3</v>
@@ -16162,12 +16178,12 @@
         <v>46207.268252314818</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6">
       <c r="A661" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B661" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="C661">
         <v>3</v>
@@ -16182,12 +16198,12 @@
         <v>46186.291863425926</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6">
       <c r="A662" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B662" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
       <c r="C662">
         <v>3</v>
@@ -16202,12 +16218,12 @@
         <v>46213.625972222224</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6">
       <c r="A663" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B663" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="C663">
         <v>2</v>
@@ -16222,12 +16238,12 @@
         <v>46210.739050925928</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6">
       <c r="A664" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B664" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="C664">
         <v>2</v>
@@ -16242,12 +16258,12 @@
         <v>46223.636886574073</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6">
       <c r="A665" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B665" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="C665">
         <v>1</v>
@@ -16262,12 +16278,12 @@
         <v>46172.285763888889</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6">
       <c r="A666" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B666" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="C666">
         <v>1</v>
@@ -16282,12 +16298,12 @@
         <v>46174.657789351855</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6">
       <c r="A667" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B667" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="C667">
         <v>1</v>
@@ -16302,12 +16318,12 @@
         <v>46149.371898148151</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6">
       <c r="A668" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B668" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="C668">
         <v>1</v>
@@ -16322,12 +16338,12 @@
         <v>46151.272418981483</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6">
       <c r="A669" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B669" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="C669">
         <v>1</v>
@@ -16342,12 +16358,12 @@
         <v>46172.263368055559</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6">
       <c r="A670" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B670" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
       <c r="C670">
         <v>1</v>
@@ -16362,12 +16378,12 @@
         <v>46147.595254629632</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6">
       <c r="A671" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B671" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="C671">
         <v>1</v>
@@ -16382,12 +16398,12 @@
         <v>46193.292615740742</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6">
       <c r="A672" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B672" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="C672">
         <v>1</v>
@@ -16402,12 +16418,12 @@
         <v>46207.274247685185</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6">
       <c r="A673" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B673" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="C673">
         <v>1</v>
@@ -16422,12 +16438,12 @@
         <v>46205.571701388886</v>
       </c>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:6">
       <c r="A674" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B674" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="C674">
         <v>1</v>
@@ -16442,12 +16458,12 @@
         <v>46198.257592592592</v>
       </c>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:6">
       <c r="A675" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B675" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="C675">
         <v>1</v>
@@ -16462,12 +16478,12 @@
         <v>46149.370625000003</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6">
       <c r="A676" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B676" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="C676">
         <v>1</v>
@@ -16482,12 +16498,12 @@
         <v>46165.373425925929</v>
       </c>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:6">
       <c r="A677" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B677" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="C677">
         <v>0</v>
@@ -16502,12 +16518,12 @@
         <v>46155.667280092595</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6">
       <c r="A678" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B678" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="C678">
         <v>0</v>
@@ -16522,12 +16538,12 @@
         <v>46161.843182870369</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6">
       <c r="A679" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B679" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="C679">
         <v>0</v>
@@ -16542,12 +16558,12 @@
         <v>46162.687662037039</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6">
       <c r="A680" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B680" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="C680">
         <v>0</v>
@@ -16562,12 +16578,12 @@
         <v>46162.536851851852</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6">
       <c r="A681" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B681" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="C681">
         <v>0</v>
